--- a/Data Analysis/1_Data/carbon+bulk_dominance_2002+2017.xlsx
+++ b/Data Analysis/1_Data/carbon+bulk_dominance_2002+2017.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:K94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,50 +367,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>r.Sr</t>
+          <t>Corg17</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Corg17</t>
+          <t>sowndiv</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>sowndiv</t>
+          <t>Corg02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Corg02</t>
+          <t>Bulk02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Bulk02</t>
+          <t>dom17_bulk</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>dom17_bulk</t>
+          <t>Corg_diff</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Corg_diff</t>
+          <t>Corg02_val</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Corg02_val</t>
+          <t>Corg17_val</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Corg17_val</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Corg_val_diff</t>
         </is>
@@ -429,37 +424,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>20.195499999999999</t>
         </is>
       </c>
+      <c r="D2">
+        <v>6</v>
+      </c>
       <c r="E2">
-        <v>6</v>
+        <v>17.20666666666667</v>
       </c>
       <c r="F2">
-        <v>17.20666666666667</v>
+        <v>1.293333333333333</v>
       </c>
       <c r="G2">
-        <v>1.293333333333333</v>
+        <v>1.303333333333333</v>
       </c>
       <c r="H2">
-        <v>1.301666666666667</v>
+        <v>0.1992555555555552</v>
       </c>
       <c r="I2">
-        <v>0.1992555555555552</v>
+        <v>73304.52960000002</v>
       </c>
       <c r="J2">
-        <v>73304.52960000002</v>
+        <v>86702.91668999998</v>
       </c>
       <c r="K2">
-        <v>86592.04339499999</v>
-      </c>
-      <c r="L2">
-        <v>885.8342529999975</v>
+        <v>893.2258059999973</v>
       </c>
     </row>
     <row r="3">
@@ -475,37 +465,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>21.733000000000001</t>
         </is>
       </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
       <c r="E3">
-        <v>6</v>
+        <v>17.86666666666667</v>
       </c>
       <c r="F3">
-        <v>17.86666666666667</v>
+        <v>1.291083333333333</v>
       </c>
       <c r="G3">
-        <v>1.291083333333333</v>
+        <v>1.2875</v>
       </c>
       <c r="H3">
-        <v>1.328333333333333</v>
+        <v>0.2577555555555556</v>
       </c>
       <c r="I3">
-        <v>0.2577555555555556</v>
+        <v>75983.8692</v>
       </c>
       <c r="J3">
-        <v>75983.8692</v>
+        <v>92170.19632500001</v>
       </c>
       <c r="K3">
-        <v>95093.39349000002</v>
-      </c>
-      <c r="L3">
-        <v>1273.968286000001</v>
+        <v>1079.088475000001</v>
       </c>
     </row>
     <row r="4">
@@ -521,37 +506,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>17.558499999999999</t>
         </is>
       </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
       <c r="E4">
-        <v>6</v>
+        <v>16.00166666666667</v>
       </c>
       <c r="F4">
-        <v>16.00166666666667</v>
+        <v>1.308333333333334</v>
       </c>
       <c r="G4">
-        <v>1.308333333333334</v>
+        <v>1.303333333333333</v>
       </c>
       <c r="H4">
-        <v>1.293333333333333</v>
+        <v>0.1037888888888889</v>
       </c>
       <c r="I4">
-        <v>0.1037888888888889</v>
+        <v>68961.58275000002</v>
       </c>
       <c r="J4">
-        <v>68961.58275000002</v>
+        <v>75381.80102999999</v>
       </c>
       <c r="K4">
-        <v>74803.42403999997</v>
-      </c>
-      <c r="L4">
-        <v>389.4560859999968</v>
+        <v>428.0145519999981</v>
       </c>
     </row>
     <row r="5">
@@ -567,37 +547,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>18.654</t>
         </is>
       </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
       <c r="E5">
-        <v>2</v>
+        <v>19.3325</v>
       </c>
       <c r="F5">
-        <v>19.3325</v>
+        <v>1.308333333333334</v>
       </c>
       <c r="G5">
-        <v>1.308333333333334</v>
+        <v>1.316666666666667</v>
       </c>
       <c r="H5">
-        <v>1.308333333333333</v>
+        <v>-0.04523333333333308</v>
       </c>
       <c r="I5">
-        <v>-0.04523333333333308</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="J5">
-        <v>83316.30862500001</v>
+        <v>80904.26339999998</v>
       </c>
       <c r="K5">
-        <v>80392.2111</v>
-      </c>
-      <c r="L5">
-        <v>-194.9398350000003</v>
+        <v>-160.8030150000016</v>
       </c>
     </row>
     <row r="6">
@@ -613,37 +588,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>18.6905</t>
         </is>
       </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
       <c r="E6">
-        <v>1</v>
+        <v>19.39058333333333</v>
       </c>
       <c r="F6">
-        <v>19.39058333333333</v>
+        <v>1.266083333333333</v>
       </c>
       <c r="G6">
-        <v>1.266083333333333</v>
+        <v>1.291666666666667</v>
       </c>
       <c r="H6">
-        <v>1.313333333333333</v>
+        <v>-0.04667222222222212</v>
       </c>
       <c r="I6">
-        <v>-0.04667222222222212</v>
+        <v>80868.01089412501</v>
       </c>
       <c r="J6">
-        <v>80868.01089412501</v>
+        <v>79523.40487500001</v>
       </c>
       <c r="K6">
-        <v>80857.34586</v>
-      </c>
-      <c r="L6">
-        <v>-0.7110022750004039</v>
+        <v>-89.64040127499999</v>
       </c>
     </row>
     <row r="7">
@@ -659,37 +629,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>21.55</t>
         </is>
       </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
       <c r="E7">
-        <v>2</v>
+        <v>19.39058333333333</v>
       </c>
       <c r="F7">
-        <v>19.39058333333333</v>
+        <v>1.266083333333333</v>
       </c>
       <c r="G7">
-        <v>1.266083333333333</v>
+        <v>1.291666666666667</v>
       </c>
       <c r="H7">
-        <v>1.313333333333333</v>
+        <v>0.1439611111111113</v>
       </c>
       <c r="I7">
-        <v>0.1439611111111113</v>
+        <v>80868.01089412501</v>
       </c>
       <c r="J7">
-        <v>80868.01089412501</v>
+        <v>91689.86250000002</v>
       </c>
       <c r="K7">
-        <v>93227.886</v>
-      </c>
-      <c r="L7">
-        <v>823.9916737249994</v>
+        <v>721.4567737250006</v>
       </c>
     </row>
     <row r="8">
@@ -705,37 +670,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
           <t>19.384499999999999</t>
         </is>
       </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
       <c r="E8">
-        <v>1</v>
+        <v>19.39058333333333</v>
       </c>
       <c r="F8">
-        <v>19.39058333333333</v>
+        <v>1.266083333333333</v>
       </c>
       <c r="G8">
-        <v>1.266083333333333</v>
+        <v>1.291666666666667</v>
       </c>
       <c r="H8">
-        <v>1.313333333333333</v>
+        <v>-0.0004055555555555183</v>
       </c>
       <c r="I8">
-        <v>-0.0004055555555555183</v>
+        <v>80868.01089412501</v>
       </c>
       <c r="J8">
-        <v>80868.01089412501</v>
+        <v>82476.201375</v>
       </c>
       <c r="K8">
-        <v>83859.67314</v>
-      </c>
-      <c r="L8">
-        <v>199.4441497249994</v>
+        <v>107.2126987249998</v>
       </c>
     </row>
     <row r="9">
@@ -751,37 +711,32 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>20.492000000000001</t>
         </is>
       </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
       <c r="E9">
-        <v>2</v>
+        <v>19.98283333333333</v>
       </c>
       <c r="F9">
-        <v>19.98283333333333</v>
+        <v>1.266083333333333</v>
       </c>
       <c r="G9">
-        <v>1.266083333333333</v>
+        <v>1.289166666666667</v>
       </c>
       <c r="H9">
-        <v>1.273333333333333</v>
+        <v>0.0339444444444446</v>
       </c>
       <c r="I9">
-        <v>0.0339444444444446</v>
+        <v>83337.97678575001</v>
       </c>
       <c r="J9">
-        <v>83337.97678575001</v>
+        <v>87019.58537999999</v>
       </c>
       <c r="K9">
-        <v>85950.82512000001</v>
-      </c>
-      <c r="L9">
-        <v>174.1898889499998</v>
+        <v>245.4405729499985</v>
       </c>
     </row>
     <row r="10">
@@ -797,37 +752,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>22.68</t>
         </is>
       </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
       <c r="E10">
-        <v>2</v>
+        <v>19.98283333333333</v>
       </c>
       <c r="F10">
-        <v>19.98283333333333</v>
+        <v>1.266083333333333</v>
       </c>
       <c r="G10">
-        <v>1.266083333333333</v>
+        <v>1.289166666666667</v>
       </c>
       <c r="H10">
-        <v>1.273333333333333</v>
+        <v>0.1798111111111112</v>
       </c>
       <c r="I10">
-        <v>0.1798111111111112</v>
+        <v>83337.97678575001</v>
       </c>
       <c r="J10">
-        <v>83337.97678575001</v>
+        <v>96310.9602</v>
       </c>
       <c r="K10">
-        <v>95128.08479999998</v>
-      </c>
-      <c r="L10">
-        <v>786.007200949998</v>
+        <v>864.8655609499993</v>
       </c>
     </row>
     <row r="11">
@@ -843,37 +793,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>25.6675</t>
         </is>
       </c>
+      <c r="D11">
+        <v>9</v>
+      </c>
       <c r="E11">
-        <v>9</v>
+        <v>21.23166666666667</v>
       </c>
       <c r="F11">
-        <v>21.23166666666667</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G11">
-        <v>1.284666666666667</v>
+        <v>1.298333333333333</v>
       </c>
       <c r="H11">
-        <v>1.373333333333333</v>
+        <v>0.2957222222222221</v>
       </c>
       <c r="I11">
-        <v>0.2957222222222221</v>
+        <v>89845.87398000002</v>
       </c>
       <c r="J11">
-        <v>89845.87398000002</v>
+        <v>109772.453925</v>
       </c>
       <c r="K11">
-        <v>116113.6098</v>
-      </c>
-      <c r="L11">
-        <v>1751.182387999999</v>
+        <v>1328.438662999998</v>
       </c>
     </row>
     <row r="12">
@@ -889,37 +834,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
           <t>20.0715</t>
         </is>
       </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
       <c r="E12">
-        <v>1</v>
+        <v>21.07</v>
       </c>
       <c r="F12">
-        <v>21.07</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G12">
-        <v>1.284666666666667</v>
+        <v>1.264166666666667</v>
       </c>
       <c r="H12">
-        <v>1.285</v>
+        <v>-0.06656666666666666</v>
       </c>
       <c r="I12">
-        <v>-0.06656666666666666</v>
+        <v>89161.75044</v>
       </c>
       <c r="J12">
-        <v>89161.75044</v>
+        <v>83581.03779749999</v>
       </c>
       <c r="K12">
-        <v>84958.444485</v>
-      </c>
-      <c r="L12">
-        <v>-280.2203970000002</v>
+        <v>-372.0475095000011</v>
       </c>
     </row>
     <row r="13">
@@ -935,37 +875,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
           <t>19.751999999999999</t>
         </is>
       </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
       <c r="E13">
-        <v>2</v>
+        <v>21.07</v>
       </c>
       <c r="F13">
-        <v>21.07</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G13">
-        <v>1.284666666666667</v>
+        <v>1.264166666666667</v>
       </c>
       <c r="H13">
-        <v>1.285</v>
+        <v>-0.08786666666666676</v>
       </c>
       <c r="I13">
-        <v>-0.08786666666666676</v>
+        <v>89161.75044</v>
       </c>
       <c r="J13">
-        <v>89161.75044</v>
+        <v>82250.58708</v>
       </c>
       <c r="K13">
-        <v>83606.06808000001</v>
-      </c>
-      <c r="L13">
-        <v>-370.3788239999994</v>
+        <v>-460.7442240000004</v>
       </c>
     </row>
     <row r="14">
@@ -981,37 +916,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
           <t>25.7285</t>
         </is>
       </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
       <c r="E14">
-        <v>6</v>
+        <v>20.94416666666667</v>
       </c>
       <c r="F14">
-        <v>20.94416666666667</v>
+        <v>1.245583333333333</v>
       </c>
       <c r="G14">
-        <v>1.245583333333333</v>
+        <v>1.225833333333333</v>
       </c>
       <c r="H14">
-        <v>1.256666666666667</v>
+        <v>0.3189555555555555</v>
       </c>
       <c r="I14">
-        <v>0.3189555555555555</v>
+        <v>85932.90004125002</v>
       </c>
       <c r="J14">
-        <v>85932.90004125002</v>
+        <v>103888.9815075</v>
       </c>
       <c r="K14">
-        <v>106502.09661</v>
-      </c>
-      <c r="L14">
-        <v>1371.279771249998</v>
+        <v>1197.072097749999</v>
       </c>
     </row>
     <row r="15">
@@ -1027,37 +957,32 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
           <t>19.684000000000001</t>
         </is>
       </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
       <c r="E15">
-        <v>1</v>
+        <v>20.05166666666666</v>
       </c>
       <c r="F15">
-        <v>20.05166666666666</v>
+        <v>1.245583333333333</v>
       </c>
       <c r="G15">
-        <v>1.245583333333333</v>
+        <v>1.2675</v>
       </c>
       <c r="H15">
-        <v>1.316666666666667</v>
+        <v>-0.02451111111111075</v>
       </c>
       <c r="I15">
-        <v>-0.02451111111111075</v>
+        <v>82271.01582750001</v>
       </c>
       <c r="J15">
-        <v>82271.01582750001</v>
+        <v>82183.55418000001</v>
       </c>
       <c r="K15">
-        <v>85371.4764</v>
-      </c>
-      <c r="L15">
-        <v>206.697371499999</v>
+        <v>-5.830776500000502</v>
       </c>
     </row>
     <row r="16">
@@ -1073,37 +998,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
           <t>22.021000000000001</t>
         </is>
       </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
       <c r="E16">
-        <v>2</v>
+        <v>20.05166666666666</v>
       </c>
       <c r="F16">
-        <v>20.05166666666666</v>
+        <v>1.245583333333333</v>
       </c>
       <c r="G16">
-        <v>1.245583333333333</v>
+        <v>1.2675</v>
       </c>
       <c r="H16">
-        <v>1.316666666666667</v>
+        <v>0.1312888888888892</v>
       </c>
       <c r="I16">
-        <v>0.1312888888888892</v>
+        <v>82271.01582750001</v>
       </c>
       <c r="J16">
-        <v>82271.01582750001</v>
+        <v>91940.86804499998</v>
       </c>
       <c r="K16">
-        <v>95507.2791</v>
-      </c>
-      <c r="L16">
-        <v>882.417551499999</v>
+        <v>644.6568144999978</v>
       </c>
     </row>
     <row r="17">
@@ -1119,37 +1039,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
           <t>23.359000000000002</t>
         </is>
       </c>
+      <c r="D17">
+        <v>6</v>
+      </c>
       <c r="E17">
-        <v>6</v>
+        <v>20.05166666666666</v>
       </c>
       <c r="F17">
-        <v>20.05166666666666</v>
+        <v>1.245583333333333</v>
       </c>
       <c r="G17">
-        <v>1.245583333333333</v>
+        <v>1.2675</v>
       </c>
       <c r="H17">
-        <v>1.316666666666667</v>
+        <v>0.2204888888888893</v>
       </c>
       <c r="I17">
-        <v>0.2204888888888893</v>
+        <v>82271.01582750001</v>
       </c>
       <c r="J17">
-        <v>82271.01582750001</v>
+        <v>97527.21205500001</v>
       </c>
       <c r="K17">
-        <v>101310.3189</v>
-      </c>
-      <c r="L17">
-        <v>1269.2868715</v>
+        <v>1017.0797485</v>
       </c>
     </row>
     <row r="18">
@@ -1165,36 +1080,31 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
           <t>24.838000000000001</t>
         </is>
       </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
       <c r="E18">
-        <v>2</v>
+        <v>19.36125</v>
       </c>
       <c r="F18">
-        <v>19.36125</v>
+        <v>1.181833333333334</v>
       </c>
       <c r="G18">
-        <v>1.181833333333334</v>
+        <v>1.173333333333333</v>
       </c>
       <c r="H18">
-        <v>1.173333333333333</v>
+        <v>0.3651166666666669</v>
       </c>
       <c r="I18">
-        <v>0.3651166666666669</v>
+        <v>75372.55243875</v>
       </c>
       <c r="J18">
-        <v>75372.55243875</v>
+        <v>95997.87648000001</v>
       </c>
       <c r="K18">
-        <v>95997.87648000001</v>
-      </c>
-      <c r="L18">
         <v>1375.02160275</v>
       </c>
     </row>
@@ -1211,37 +1121,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
           <t>17.941500000000001</t>
         </is>
       </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
       <c r="E19">
-        <v>2</v>
+        <v>17.86666666666667</v>
       </c>
       <c r="F19">
-        <v>17.86666666666667</v>
+        <v>1.291083333333333</v>
       </c>
       <c r="G19">
-        <v>1.291083333333333</v>
+        <v>1.2875</v>
       </c>
       <c r="H19">
-        <v>1.328333333333333</v>
+        <v>0.004988888888888946</v>
       </c>
       <c r="I19">
-        <v>0.004988888888888946</v>
+        <v>75983.8692</v>
       </c>
       <c r="J19">
-        <v>75983.8692</v>
+        <v>76090.35003750001</v>
       </c>
       <c r="K19">
-        <v>78503.571495</v>
-      </c>
-      <c r="L19">
-        <v>167.9801529999997</v>
+        <v>7.098722500000926</v>
       </c>
     </row>
     <row r="20">
@@ -1257,37 +1162,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
           <t>17.323499999999999</t>
         </is>
       </c>
+      <c r="D20">
+        <v>2</v>
+      </c>
       <c r="E20">
-        <v>2</v>
+        <v>16.00166666666667</v>
       </c>
       <c r="F20">
-        <v>16.00166666666667</v>
+        <v>1.308333333333334</v>
       </c>
       <c r="G20">
-        <v>1.308333333333334</v>
+        <v>1.303333333333333</v>
       </c>
       <c r="H20">
-        <v>1.293333333333333</v>
+        <v>0.08812222222222227</v>
       </c>
       <c r="I20">
-        <v>0.08812222222222227</v>
+        <v>68961.58275000002</v>
       </c>
       <c r="J20">
-        <v>68961.58275000002</v>
+        <v>74372.90372999999</v>
       </c>
       <c r="K20">
-        <v>73802.26763999999</v>
-      </c>
-      <c r="L20">
-        <v>322.7123259999983</v>
+        <v>360.7547319999983</v>
       </c>
     </row>
     <row r="21">
@@ -1303,37 +1203,32 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
           <t>23.330500000000001</t>
         </is>
       </c>
+      <c r="D21">
+        <v>9</v>
+      </c>
       <c r="E21">
-        <v>9</v>
+        <v>19.3325</v>
       </c>
       <c r="F21">
-        <v>19.3325</v>
+        <v>1.308333333333334</v>
       </c>
       <c r="G21">
-        <v>1.308333333333334</v>
+        <v>1.316666666666667</v>
       </c>
       <c r="H21">
-        <v>1.308333333333333</v>
+        <v>0.2665333333333336</v>
       </c>
       <c r="I21">
-        <v>0.2665333333333336</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="J21">
-        <v>83316.30862500001</v>
+        <v>101186.71155</v>
       </c>
       <c r="K21">
-        <v>100546.289325</v>
-      </c>
-      <c r="L21">
-        <v>1148.66538</v>
+        <v>1191.360195</v>
       </c>
     </row>
     <row r="22">
@@ -1349,37 +1244,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
           <t>24.769500000000001</t>
         </is>
       </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
       <c r="E22">
-        <v>2</v>
+        <v>19.3325</v>
       </c>
       <c r="F22">
-        <v>19.3325</v>
+        <v>1.308333333333334</v>
       </c>
       <c r="G22">
-        <v>1.308333333333334</v>
+        <v>1.316666666666667</v>
       </c>
       <c r="H22">
-        <v>1.308333333333333</v>
+        <v>0.362466666666667</v>
       </c>
       <c r="I22">
-        <v>0.362466666666667</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="J22">
-        <v>83316.30862500001</v>
+        <v>107427.79845</v>
       </c>
       <c r="K22">
-        <v>106747.875675</v>
-      </c>
-      <c r="L22">
-        <v>1562.104469999999</v>
+        <v>1607.432655</v>
       </c>
     </row>
     <row r="23">
@@ -1395,37 +1285,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
           <t>17.1615</t>
         </is>
       </c>
+      <c r="D23">
+        <v>2</v>
+      </c>
       <c r="E23">
-        <v>2</v>
+        <v>19.3325</v>
       </c>
       <c r="F23">
-        <v>19.3325</v>
+        <v>1.308333333333334</v>
       </c>
       <c r="G23">
-        <v>1.308333333333334</v>
+        <v>1.316666666666667</v>
       </c>
       <c r="H23">
-        <v>1.308333333333333</v>
+        <v>-0.144733333333333</v>
       </c>
       <c r="I23">
-        <v>-0.144733333333333</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="J23">
-        <v>83316.30862500001</v>
+        <v>74431.14165000001</v>
       </c>
       <c r="K23">
-        <v>73960.058475</v>
-      </c>
-      <c r="L23">
-        <v>-623.7500100000004</v>
+        <v>-592.344465</v>
       </c>
     </row>
     <row r="24">
@@ -1441,37 +1326,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
           <t>25.017499999999998</t>
         </is>
       </c>
+      <c r="D24">
+        <v>6</v>
+      </c>
       <c r="E24">
-        <v>6</v>
+        <v>21.23166666666667</v>
       </c>
       <c r="F24">
-        <v>21.23166666666667</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G24">
-        <v>1.284666666666667</v>
+        <v>1.298333333333333</v>
       </c>
       <c r="H24">
-        <v>1.373333333333333</v>
+        <v>0.2523888888888886</v>
       </c>
       <c r="I24">
-        <v>0.2523888888888886</v>
+        <v>89845.87398000002</v>
       </c>
       <c r="J24">
-        <v>89845.87398000002</v>
+        <v>106992.592425</v>
       </c>
       <c r="K24">
-        <v>113173.1658</v>
-      </c>
-      <c r="L24">
-        <v>1555.152787999998</v>
+        <v>1143.114562999998</v>
       </c>
     </row>
     <row r="25">
@@ -1487,37 +1367,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
           <t>26.083500000000001</t>
         </is>
       </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
       <c r="E25">
-        <v>2</v>
+        <v>21.23166666666667</v>
       </c>
       <c r="F25">
-        <v>21.23166666666667</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G25">
-        <v>1.284666666666667</v>
+        <v>1.298333333333333</v>
       </c>
       <c r="H25">
-        <v>1.373333333333333</v>
+        <v>0.3234555555555554</v>
       </c>
       <c r="I25">
-        <v>0.3234555555555554</v>
+        <v>89845.87398000002</v>
       </c>
       <c r="J25">
-        <v>89845.87398000002</v>
+        <v>111551.565285</v>
       </c>
       <c r="K25">
-        <v>117995.49396</v>
-      </c>
-      <c r="L25">
-        <v>1876.641331999999</v>
+        <v>1447.046086999999</v>
       </c>
     </row>
     <row r="26">
@@ -1533,37 +1408,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
           <t>23.3415</t>
         </is>
       </c>
+      <c r="D26">
+        <v>2</v>
+      </c>
       <c r="E26">
-        <v>2</v>
+        <v>21.07</v>
       </c>
       <c r="F26">
-        <v>21.07</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G26">
-        <v>1.284666666666667</v>
+        <v>1.264166666666667</v>
       </c>
       <c r="H26">
-        <v>1.285</v>
+        <v>0.1514333333333333</v>
       </c>
       <c r="I26">
-        <v>0.1514333333333333</v>
+        <v>89161.75044</v>
       </c>
       <c r="J26">
-        <v>89161.75044</v>
+        <v>97197.8573475</v>
       </c>
       <c r="K26">
-        <v>98799.667785</v>
-      </c>
-      <c r="L26">
-        <v>642.5278229999997</v>
+        <v>535.7404604999998</v>
       </c>
     </row>
     <row r="27">
@@ -1579,37 +1449,32 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
           <t>23.945499999999999</t>
         </is>
       </c>
+      <c r="D27">
+        <v>2</v>
+      </c>
       <c r="E27">
-        <v>2</v>
+        <v>21.07</v>
       </c>
       <c r="F27">
-        <v>21.07</v>
+        <v>1.284666666666667</v>
       </c>
       <c r="G27">
-        <v>1.284666666666667</v>
+        <v>1.264166666666667</v>
       </c>
       <c r="H27">
-        <v>1.285</v>
+        <v>0.1916999999999999</v>
       </c>
       <c r="I27">
-        <v>0.1916999999999999</v>
+        <v>89161.75044</v>
       </c>
       <c r="J27">
-        <v>89161.75044</v>
+        <v>99713.01300749999</v>
       </c>
       <c r="K27">
-        <v>101356.272945</v>
-      </c>
-      <c r="L27">
-        <v>812.968167000001</v>
+        <v>703.4175044999992</v>
       </c>
     </row>
     <row r="28">
@@ -1625,37 +1490,32 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
           <t>18.670999999999999</t>
         </is>
       </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
       <c r="E28">
-        <v>2</v>
+        <v>18.78166666666667</v>
       </c>
       <c r="F28">
-        <v>18.78166666666667</v>
+        <v>1.26975</v>
       </c>
       <c r="G28">
-        <v>1.26975</v>
+        <v>1.2975</v>
       </c>
       <c r="H28">
-        <v>1.265</v>
+        <v>-0.007377777777777794</v>
       </c>
       <c r="I28">
-        <v>-0.007377777777777794</v>
+        <v>78555.38199750001</v>
       </c>
       <c r="J28">
-        <v>78555.38199750001</v>
+        <v>79799.20051499999</v>
       </c>
       <c r="K28">
-        <v>77800.37660999999</v>
-      </c>
-      <c r="L28">
-        <v>-50.33369250000105</v>
+        <v>82.92123449999877</v>
       </c>
     </row>
     <row r="29">
@@ -1671,37 +1531,32 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
           <t>22.815000000000001</t>
         </is>
       </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
       <c r="E29">
-        <v>9</v>
+        <v>18.78166666666667</v>
       </c>
       <c r="F29">
-        <v>18.78166666666667</v>
+        <v>1.26975</v>
       </c>
       <c r="G29">
-        <v>1.26975</v>
+        <v>1.2975</v>
       </c>
       <c r="H29">
-        <v>1.265</v>
+        <v>0.268888888888889</v>
       </c>
       <c r="I29">
-        <v>0.268888888888889</v>
+        <v>78555.38199750001</v>
       </c>
       <c r="J29">
-        <v>78555.38199750001</v>
+        <v>97510.51147500002</v>
       </c>
       <c r="K29">
-        <v>95068.05164999999</v>
-      </c>
-      <c r="L29">
-        <v>1100.844643499999</v>
+        <v>1263.675298500001</v>
       </c>
     </row>
     <row r="30">
@@ -1717,37 +1572,32 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
           <t>18.447500000000002</t>
         </is>
       </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
       <c r="E30">
-        <v>2</v>
+        <v>18.78166666666667</v>
       </c>
       <c r="F30">
-        <v>18.78166666666667</v>
+        <v>1.26975</v>
       </c>
       <c r="G30">
-        <v>1.26975</v>
+        <v>1.2975</v>
       </c>
       <c r="H30">
-        <v>1.265</v>
+        <v>-0.02227777777777765</v>
       </c>
       <c r="I30">
-        <v>-0.02227777777777765</v>
+        <v>78555.38199750001</v>
       </c>
       <c r="J30">
-        <v>78555.38199750001</v>
+        <v>78843.96933750001</v>
       </c>
       <c r="K30">
-        <v>76869.07222500003</v>
-      </c>
-      <c r="L30">
-        <v>-112.4206514999988</v>
+        <v>19.23915599999988</v>
       </c>
     </row>
     <row r="31">
@@ -1763,37 +1613,32 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
           <t>21.3415</t>
         </is>
       </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
       <c r="E31">
-        <v>2</v>
+        <v>18.69708333333333</v>
       </c>
       <c r="F31">
-        <v>18.69708333333333</v>
+        <v>1.3415</v>
       </c>
       <c r="G31">
-        <v>1.3415</v>
+        <v>1.279166666666667</v>
       </c>
       <c r="H31">
-        <v>1.241666666666667</v>
+        <v>0.1762944444444446</v>
       </c>
       <c r="I31">
-        <v>0.1762944444444446</v>
+        <v>82620.56023875</v>
       </c>
       <c r="J31">
-        <v>82620.56023875</v>
+        <v>89924.01086250001</v>
       </c>
       <c r="K31">
-        <v>87287.80207500003</v>
-      </c>
-      <c r="L31">
-        <v>311.1494557500021</v>
+        <v>486.8967082500012</v>
       </c>
     </row>
     <row r="32">
@@ -1809,37 +1654,32 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
           <t>17.331499999999998</t>
         </is>
       </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
       <c r="E32">
-        <v>1</v>
+        <v>20.30675</v>
       </c>
       <c r="F32">
-        <v>20.30675</v>
+        <v>1.303916666666667</v>
       </c>
       <c r="G32">
-        <v>1.303916666666667</v>
+        <v>1.266666666666667</v>
       </c>
       <c r="H32">
-        <v>1.271666666666667</v>
+        <v>-0.1983500000000004</v>
       </c>
       <c r="I32">
-        <v>-0.1983500000000004</v>
+        <v>87219.55238512503</v>
       </c>
       <c r="J32">
-        <v>87219.55238512503</v>
+        <v>72313.9506</v>
       </c>
       <c r="K32">
-        <v>72599.40040499999</v>
-      </c>
-      <c r="L32">
-        <v>-974.6767986750026</v>
+        <v>-993.7067856750024</v>
       </c>
     </row>
     <row r="33">
@@ -1855,37 +1695,32 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
           <t>24.712</t>
         </is>
       </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
       <c r="E33">
-        <v>2</v>
+        <v>22.105</v>
       </c>
       <c r="F33">
-        <v>22.105</v>
+        <v>1.303916666666667</v>
       </c>
       <c r="G33">
-        <v>1.303916666666667</v>
+        <v>1.2425</v>
       </c>
       <c r="H33">
-        <v>1.228333333333333</v>
+        <v>0.1738</v>
       </c>
       <c r="I33">
-        <v>0.1738</v>
+        <v>94943.21865750001</v>
       </c>
       <c r="J33">
-        <v>94943.21865750001</v>
+        <v>101141.15004</v>
       </c>
       <c r="K33">
-        <v>99987.96455999999</v>
-      </c>
-      <c r="L33">
-        <v>336.316393499999</v>
+        <v>413.195425499999</v>
       </c>
     </row>
     <row r="34">
@@ -1901,37 +1736,32 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
           <t>22.5245</t>
         </is>
       </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
       <c r="E34">
-        <v>2</v>
+        <v>19.25875</v>
       </c>
       <c r="F34">
-        <v>19.25875</v>
+        <v>1.283833333333333</v>
       </c>
       <c r="G34">
-        <v>1.283833333333333</v>
+        <v>1.261666666666667</v>
       </c>
       <c r="H34">
-        <v>1.241666666666667</v>
+        <v>0.2177166666666667</v>
       </c>
       <c r="I34">
-        <v>0.2177166666666667</v>
+        <v>81444.23303624999</v>
       </c>
       <c r="J34">
-        <v>81444.23303624999</v>
+        <v>93610.24528500001</v>
       </c>
       <c r="K34">
-        <v>92126.331225</v>
-      </c>
-      <c r="L34">
-        <v>712.1398792500006</v>
+        <v>811.0674832500013</v>
       </c>
     </row>
     <row r="35">
@@ -1947,37 +1777,32 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
           <t>20.411000000000001</t>
         </is>
       </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
       <c r="E35">
-        <v>2</v>
+        <v>20.76166666666667</v>
       </c>
       <c r="F35">
-        <v>20.76166666666667</v>
+        <v>1.283833333333333</v>
       </c>
       <c r="G35">
-        <v>1.283833333333333</v>
+        <v>1.229166666666667</v>
       </c>
       <c r="H35">
-        <v>1.198333333333333</v>
+        <v>-0.02337777777777793</v>
       </c>
       <c r="I35">
-        <v>-0.02337777777777793</v>
+        <v>87799.98796500004</v>
       </c>
       <c r="J35">
-        <v>87799.98796500004</v>
+        <v>82641.58762499999</v>
       </c>
       <c r="K35">
-        <v>80568.54440999999</v>
-      </c>
-      <c r="L35">
-        <v>-482.0962370000033</v>
+        <v>-343.8933560000034</v>
       </c>
     </row>
     <row r="36">
@@ -1993,37 +1818,32 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
           <t>28.137499999999999</t>
         </is>
       </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
       <c r="E36">
-        <v>6</v>
+        <v>22.41708333333333</v>
       </c>
       <c r="F36">
-        <v>22.41708333333333</v>
+        <v>1.230333333333334</v>
       </c>
       <c r="G36">
-        <v>1.230333333333334</v>
+        <v>1.263333333333333</v>
       </c>
       <c r="H36">
-        <v>1.26</v>
+        <v>0.3813611111111113</v>
       </c>
       <c r="I36">
-        <v>0.3813611111111113</v>
+        <v>90850.11713249999</v>
       </c>
       <c r="J36">
-        <v>90850.11713249999</v>
+        <v>117091.95525</v>
       </c>
       <c r="K36">
-        <v>116783.0055</v>
-      </c>
-      <c r="L36">
-        <v>1728.859224500001</v>
+        <v>1749.455874500002</v>
       </c>
     </row>
     <row r="37">
@@ -2039,37 +1859,32 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
           <t>20.747499999999999</t>
         </is>
       </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
       <c r="E37">
-        <v>1</v>
+        <v>22.77125</v>
       </c>
       <c r="F37">
-        <v>22.77125</v>
+        <v>1.230333333333334</v>
       </c>
       <c r="G37">
-        <v>1.230333333333334</v>
+        <v>1.230833333333333</v>
       </c>
       <c r="H37">
-        <v>1.226666666666667</v>
+        <v>-0.1349166666666669</v>
       </c>
       <c r="I37">
-        <v>-0.1349166666666669</v>
+        <v>92285.45475750002</v>
       </c>
       <c r="J37">
-        <v>92285.45475750002</v>
+        <v>84117.93783750001</v>
       </c>
       <c r="K37">
-        <v>83833.1784</v>
-      </c>
-      <c r="L37">
-        <v>-563.4850905000009</v>
+        <v>-544.5011280000006</v>
       </c>
     </row>
     <row r="38">
@@ -2085,37 +1900,32 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
           <t>18.805</t>
         </is>
       </c>
+      <c r="D38">
+        <v>2</v>
+      </c>
       <c r="E38">
-        <v>2</v>
+        <v>23.425</v>
       </c>
       <c r="F38">
-        <v>23.425</v>
+        <v>1.181833333333334</v>
       </c>
       <c r="G38">
-        <v>1.181833333333334</v>
+        <v>1.181666666666667</v>
       </c>
       <c r="H38">
-        <v>1.165</v>
+        <v>-0.3079999999999998</v>
       </c>
       <c r="I38">
-        <v>-0.3079999999999998</v>
+        <v>91192.56457500003</v>
       </c>
       <c r="J38">
-        <v>91192.56457500003</v>
+        <v>73196.77004999999</v>
       </c>
       <c r="K38">
-        <v>72164.37555</v>
-      </c>
-      <c r="L38">
-        <v>-1268.545935000002</v>
+        <v>-1199.719635000002</v>
       </c>
     </row>
     <row r="39">
@@ -2131,37 +1941,32 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
           <t>28.004999999999999</t>
         </is>
       </c>
+      <c r="D39">
+        <v>6</v>
+      </c>
       <c r="E39">
-        <v>6</v>
+        <v>23.425</v>
       </c>
       <c r="F39">
-        <v>23.425</v>
+        <v>1.181833333333334</v>
       </c>
       <c r="G39">
-        <v>1.181833333333334</v>
+        <v>1.181666666666667</v>
       </c>
       <c r="H39">
-        <v>1.165</v>
+        <v>0.3053333333333335</v>
       </c>
       <c r="I39">
-        <v>0.3053333333333335</v>
+        <v>91192.56457500003</v>
       </c>
       <c r="J39">
-        <v>91192.56457500003</v>
+        <v>109006.94205</v>
       </c>
       <c r="K39">
-        <v>107469.46755</v>
-      </c>
-      <c r="L39">
-        <v>1085.126864999998</v>
+        <v>1187.625164999997</v>
       </c>
     </row>
     <row r="40">
@@ -2177,37 +1982,32 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
           <t>18.995999999999999</t>
         </is>
       </c>
+      <c r="D40">
+        <v>1</v>
+      </c>
       <c r="E40">
-        <v>1</v>
+        <v>19.05833333333334</v>
       </c>
       <c r="F40">
-        <v>19.05833333333334</v>
+        <v>1.3415</v>
       </c>
       <c r="G40">
-        <v>1.3415</v>
+        <v>1.3</v>
       </c>
       <c r="H40">
-        <v>1.275</v>
+        <v>-0.004155555555555897</v>
       </c>
       <c r="I40">
-        <v>-0.004155555555555897</v>
+        <v>84216.88822499999</v>
       </c>
       <c r="J40">
-        <v>84216.88822499999</v>
+        <v>81344.67119999998</v>
       </c>
       <c r="K40">
-        <v>79780.35060000001</v>
-      </c>
-      <c r="L40">
-        <v>-295.7691749999988</v>
+        <v>-191.4811350000004</v>
       </c>
     </row>
     <row r="41">
@@ -2223,37 +2023,32 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
           <t>21.795500000000001</t>
         </is>
       </c>
+      <c r="D41">
+        <v>6</v>
+      </c>
       <c r="E41">
-        <v>6</v>
+        <v>19.05833333333334</v>
       </c>
       <c r="F41">
-        <v>19.05833333333334</v>
+        <v>1.3415</v>
       </c>
       <c r="G41">
-        <v>1.3415</v>
+        <v>1.3</v>
       </c>
       <c r="H41">
-        <v>1.275</v>
+        <v>0.1824777777777776</v>
       </c>
       <c r="I41">
-        <v>0.1824777777777776</v>
+        <v>84216.88822499999</v>
       </c>
       <c r="J41">
-        <v>84216.88822499999</v>
+        <v>93332.69010000001</v>
       </c>
       <c r="K41">
-        <v>91537.830675</v>
-      </c>
-      <c r="L41">
-        <v>488.0628300000011</v>
+        <v>607.7201250000013</v>
       </c>
     </row>
     <row r="42">
@@ -2269,37 +2064,32 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
           <t>20.007000000000001</t>
         </is>
       </c>
+      <c r="D42">
+        <v>6</v>
+      </c>
       <c r="E42">
-        <v>6</v>
+        <v>19.05833333333334</v>
       </c>
       <c r="F42">
-        <v>19.05833333333334</v>
+        <v>1.3415</v>
       </c>
       <c r="G42">
-        <v>1.3415</v>
+        <v>1.3</v>
       </c>
       <c r="H42">
-        <v>1.275</v>
+        <v>0.06324444444444428</v>
       </c>
       <c r="I42">
-        <v>0.06324444444444428</v>
+        <v>84216.88822499999</v>
       </c>
       <c r="J42">
-        <v>84216.88822499999</v>
+        <v>85673.97540000001</v>
       </c>
       <c r="K42">
-        <v>84026.39895000003</v>
-      </c>
-      <c r="L42">
-        <v>-12.69928499999708</v>
+        <v>97.13914500000149</v>
       </c>
     </row>
     <row r="43">
@@ -2315,37 +2105,32 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
           <t>18.722000000000001</t>
         </is>
       </c>
+      <c r="D43">
+        <v>2</v>
+      </c>
       <c r="E43">
-        <v>2</v>
+        <v>18.69708333333333</v>
       </c>
       <c r="F43">
-        <v>18.69708333333333</v>
+        <v>1.3415</v>
       </c>
       <c r="G43">
-        <v>1.3415</v>
+        <v>1.279166666666667</v>
       </c>
       <c r="H43">
-        <v>1.241666666666667</v>
+        <v>0.001661111111111306</v>
       </c>
       <c r="I43">
-        <v>0.001661111111111306</v>
+        <v>82620.56023875</v>
       </c>
       <c r="J43">
-        <v>82620.56023875</v>
+        <v>78886.55115</v>
       </c>
       <c r="K43">
-        <v>76573.91610000003</v>
-      </c>
-      <c r="L43">
-        <v>-403.1096092499977</v>
+        <v>-248.9339392499998</v>
       </c>
     </row>
     <row r="44">
@@ -2361,37 +2146,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
           <t>24.971</t>
         </is>
       </c>
+      <c r="D44">
+        <v>2</v>
+      </c>
       <c r="E44">
-        <v>2</v>
+        <v>22.105</v>
       </c>
       <c r="F44">
-        <v>22.105</v>
+        <v>1.303916666666667</v>
       </c>
       <c r="G44">
-        <v>1.303916666666667</v>
+        <v>1.2425</v>
       </c>
       <c r="H44">
-        <v>1.228333333333333</v>
+        <v>0.1910666666666666</v>
       </c>
       <c r="I44">
-        <v>0.1910666666666666</v>
+        <v>94943.21865750001</v>
       </c>
       <c r="J44">
-        <v>94943.21865750001</v>
+        <v>102201.183945</v>
       </c>
       <c r="K44">
-        <v>101035.91223</v>
-      </c>
-      <c r="L44">
-        <v>406.1795714999996</v>
+        <v>483.8643524999992</v>
       </c>
     </row>
     <row r="45">
@@ -2407,37 +2187,32 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
           <t>20.793500000000002</t>
         </is>
       </c>
+      <c r="D45">
+        <v>2</v>
+      </c>
       <c r="E45">
-        <v>2</v>
+        <v>19.25875</v>
       </c>
       <c r="F45">
-        <v>19.25875</v>
+        <v>1.283833333333333</v>
       </c>
       <c r="G45">
-        <v>1.283833333333333</v>
+        <v>1.261666666666667</v>
       </c>
       <c r="H45">
-        <v>1.241666666666667</v>
+        <v>0.1023166666666668</v>
       </c>
       <c r="I45">
-        <v>0.1023166666666668</v>
+        <v>81444.23303624999</v>
       </c>
       <c r="J45">
-        <v>81444.23303624999</v>
+        <v>86416.33045500002</v>
       </c>
       <c r="K45">
-        <v>85046.454675</v>
-      </c>
-      <c r="L45">
-        <v>240.1481092500006</v>
+        <v>331.4731612500017</v>
       </c>
     </row>
     <row r="46">
@@ -2453,37 +2228,32 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
           <t>26.34</t>
         </is>
       </c>
+      <c r="D46">
+        <v>6</v>
+      </c>
       <c r="E46">
-        <v>6</v>
+        <v>20.76166666666667</v>
       </c>
       <c r="F46">
-        <v>20.76166666666667</v>
+        <v>1.283833333333333</v>
       </c>
       <c r="G46">
-        <v>1.283833333333333</v>
+        <v>1.229166666666667</v>
       </c>
       <c r="H46">
-        <v>1.198333333333333</v>
+        <v>0.3718888888888887</v>
       </c>
       <c r="I46">
-        <v>0.3718888888888887</v>
+        <v>87799.98796500004</v>
       </c>
       <c r="J46">
-        <v>87799.98796500004</v>
+        <v>106647.3675</v>
       </c>
       <c r="K46">
-        <v>103972.1454</v>
-      </c>
-      <c r="L46">
-        <v>1078.143828999995</v>
+        <v>1256.491968999996</v>
       </c>
     </row>
     <row r="47">
@@ -2499,37 +2269,32 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
           <t>24.838999999999999</t>
         </is>
       </c>
+      <c r="D47">
+        <v>6</v>
+      </c>
       <c r="E47">
-        <v>6</v>
+        <v>22.41708333333333</v>
       </c>
       <c r="F47">
-        <v>22.41708333333333</v>
+        <v>1.230333333333334</v>
       </c>
       <c r="G47">
-        <v>1.230333333333334</v>
+        <v>1.263333333333333</v>
       </c>
       <c r="H47">
-        <v>1.26</v>
+        <v>0.1614611111111112</v>
       </c>
       <c r="I47">
-        <v>0.1614611111111112</v>
+        <v>90850.11713249999</v>
       </c>
       <c r="J47">
-        <v>90850.11713249999</v>
+        <v>103365.51138</v>
       </c>
       <c r="K47">
-        <v>103092.77916</v>
-      </c>
-      <c r="L47">
-        <v>816.1774685000012</v>
+        <v>834.3596164999996</v>
       </c>
     </row>
     <row r="48">
@@ -2545,37 +2310,32 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
           <t>25.9175</t>
         </is>
       </c>
+      <c r="D48">
+        <v>2</v>
+      </c>
       <c r="E48">
-        <v>2</v>
+        <v>22.77125</v>
       </c>
       <c r="F48">
-        <v>22.77125</v>
+        <v>1.230333333333334</v>
       </c>
       <c r="G48">
-        <v>1.230333333333334</v>
+        <v>1.230833333333333</v>
       </c>
       <c r="H48">
-        <v>1.226666666666667</v>
+        <v>0.2097499999999999</v>
       </c>
       <c r="I48">
-        <v>0.2097499999999999</v>
+        <v>92285.45475750002</v>
       </c>
       <c r="J48">
-        <v>92285.45475750002</v>
+        <v>105079.0048875</v>
       </c>
       <c r="K48">
-        <v>104723.2872</v>
-      </c>
-      <c r="L48">
-        <v>829.1888294999983</v>
+        <v>852.9033420000002</v>
       </c>
     </row>
     <row r="49">
@@ -2591,37 +2351,32 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
           <t>28.74</t>
         </is>
       </c>
+      <c r="D49">
+        <v>9</v>
+      </c>
       <c r="E49">
-        <v>9</v>
+        <v>22.77125</v>
       </c>
       <c r="F49">
-        <v>22.77125</v>
+        <v>1.230333333333334</v>
       </c>
       <c r="G49">
-        <v>1.230333333333334</v>
+        <v>1.230833333333333</v>
       </c>
       <c r="H49">
-        <v>1.226666666666667</v>
+        <v>0.3979166666666664</v>
       </c>
       <c r="I49">
-        <v>0.3979166666666664</v>
+        <v>92285.45475750002</v>
       </c>
       <c r="J49">
-        <v>92285.45475750002</v>
+        <v>116522.4501</v>
       </c>
       <c r="K49">
-        <v>116127.9936</v>
-      </c>
-      <c r="L49">
-        <v>1589.502589500001</v>
+        <v>1615.799689499999</v>
       </c>
     </row>
     <row r="50">
@@ -2637,36 +2392,31 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
           <t>20.734999999999999</t>
         </is>
       </c>
+      <c r="D50">
+        <v>2</v>
+      </c>
       <c r="E50">
-        <v>2</v>
+        <v>20.01333333333334</v>
       </c>
       <c r="F50">
-        <v>20.01333333333334</v>
+        <v>1.348</v>
       </c>
       <c r="G50">
-        <v>1.348</v>
+        <v>1.235</v>
       </c>
       <c r="H50">
-        <v>1.235</v>
+        <v>0.0481111111111107</v>
       </c>
       <c r="I50">
-        <v>0.0481111111111107</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="J50">
-        <v>88865.44416000003</v>
+        <v>84351.84615000001</v>
       </c>
       <c r="K50">
-        <v>84351.84615000001</v>
-      </c>
-      <c r="L50">
         <v>-300.906534000001</v>
       </c>
     </row>
@@ -2683,36 +2433,31 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
           <t>24.530999999999999</t>
         </is>
       </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
       <c r="E51">
-        <v>1</v>
+        <v>20.01333333333334</v>
       </c>
       <c r="F51">
-        <v>20.01333333333334</v>
+        <v>1.348</v>
       </c>
       <c r="G51">
-        <v>1.348</v>
+        <v>1.235</v>
       </c>
       <c r="H51">
-        <v>1.235</v>
+        <v>0.3011777777777773</v>
       </c>
       <c r="I51">
-        <v>0.3011777777777773</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="J51">
-        <v>88865.44416000003</v>
+        <v>99794.31579000001</v>
       </c>
       <c r="K51">
-        <v>99794.31579000001</v>
-      </c>
-      <c r="L51">
         <v>728.5914419999987</v>
       </c>
     </row>
@@ -2729,36 +2474,31 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
           <t>24.2425</t>
         </is>
       </c>
+      <c r="D52">
+        <v>2</v>
+      </c>
       <c r="E52">
-        <v>2</v>
+        <v>20.01333333333334</v>
       </c>
       <c r="F52">
-        <v>20.01333333333334</v>
+        <v>1.348</v>
       </c>
       <c r="G52">
-        <v>1.348</v>
+        <v>1.235</v>
       </c>
       <c r="H52">
-        <v>1.235</v>
+        <v>0.2819444444444441</v>
       </c>
       <c r="I52">
-        <v>0.2819444444444441</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="J52">
-        <v>88865.44416000003</v>
+        <v>98620.67182500003</v>
       </c>
       <c r="K52">
-        <v>98620.67182500003</v>
-      </c>
-      <c r="L52">
         <v>650.3485109999999</v>
       </c>
     </row>
@@ -2775,36 +2515,31 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
           <t>19.710999999999999</t>
         </is>
       </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
       <c r="E53">
-        <v>1</v>
+        <v>17.37216666666666</v>
       </c>
       <c r="F53">
-        <v>17.37216666666666</v>
+        <v>1.379</v>
       </c>
       <c r="G53">
-        <v>1.379</v>
+        <v>1.238333333333333</v>
       </c>
       <c r="H53">
-        <v>1.238333333333333</v>
+        <v>0.1559222222222225</v>
       </c>
       <c r="I53">
-        <v>0.1559222222222225</v>
+        <v>78911.78154299999</v>
       </c>
       <c r="J53">
-        <v>78911.78154299999</v>
+        <v>80402.54876999999</v>
       </c>
       <c r="K53">
-        <v>80402.54876999999</v>
-      </c>
-      <c r="L53">
         <v>99.38448180000026</v>
       </c>
     </row>
@@ -2821,36 +2556,31 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
           <t>24.027000000000001</t>
         </is>
       </c>
+      <c r="D54">
+        <v>6</v>
+      </c>
       <c r="E54">
-        <v>6</v>
+        <v>17.37216666666666</v>
       </c>
       <c r="F54">
-        <v>17.37216666666666</v>
+        <v>1.379</v>
       </c>
       <c r="G54">
-        <v>1.379</v>
+        <v>1.238333333333333</v>
       </c>
       <c r="H54">
-        <v>1.238333333333333</v>
+        <v>0.443655555555556</v>
       </c>
       <c r="I54">
-        <v>0.443655555555556</v>
+        <v>78911.78154299999</v>
       </c>
       <c r="J54">
-        <v>78911.78154299999</v>
+        <v>98007.81488999999</v>
       </c>
       <c r="K54">
-        <v>98007.81488999999</v>
-      </c>
-      <c r="L54">
         <v>1273.0688898</v>
       </c>
     </row>
@@ -2867,36 +2597,31 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
           <t>25.812999999999999</t>
         </is>
       </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
       <c r="E55">
-        <v>6</v>
+        <v>19.71116666666667</v>
       </c>
       <c r="F55">
-        <v>19.71116666666667</v>
+        <v>1.330166666666667</v>
       </c>
       <c r="G55">
-        <v>1.330166666666667</v>
+        <v>1.328333333333333</v>
       </c>
       <c r="H55">
-        <v>1.328333333333333</v>
+        <v>0.4067888888888885</v>
       </c>
       <c r="I55">
-        <v>0.4067888888888885</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="J55">
-        <v>86365.83682050004</v>
+        <v>112945.55589</v>
       </c>
       <c r="K55">
-        <v>112945.55589</v>
-      </c>
-      <c r="L55">
         <v>1771.981271299996</v>
       </c>
     </row>
@@ -2913,36 +2638,31 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
           <t>21.383500000000002</t>
         </is>
       </c>
+      <c r="D56">
+        <v>2</v>
+      </c>
       <c r="E56">
-        <v>2</v>
+        <v>20.67666666666667</v>
       </c>
       <c r="F56">
-        <v>20.67666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G56">
-        <v>1.411</v>
+        <v>1.293333333333333</v>
       </c>
       <c r="H56">
-        <v>1.293333333333333</v>
+        <v>0.04712222222222214</v>
       </c>
       <c r="I56">
-        <v>0.04712222222222214</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="J56">
-        <v>96101.71434000002</v>
+        <v>91098.84204000002</v>
       </c>
       <c r="K56">
-        <v>91098.84204000002</v>
-      </c>
-      <c r="L56">
         <v>-333.5248200000002</v>
       </c>
     </row>
@@ -2959,36 +2679,31 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
           <t>25.4755</t>
         </is>
       </c>
+      <c r="D57">
+        <v>6</v>
+      </c>
       <c r="E57">
-        <v>6</v>
+        <v>20.67666666666667</v>
       </c>
       <c r="F57">
-        <v>20.67666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G57">
-        <v>1.411</v>
+        <v>1.293333333333333</v>
       </c>
       <c r="H57">
-        <v>1.293333333333333</v>
+        <v>0.3199222222222221</v>
       </c>
       <c r="I57">
-        <v>0.3199222222222221</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="J57">
-        <v>96101.71434000002</v>
+        <v>108531.74412</v>
       </c>
       <c r="K57">
-        <v>108531.74412</v>
-      </c>
-      <c r="L57">
         <v>828.6686520000007</v>
       </c>
     </row>
@@ -3005,36 +2720,31 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
           <t>22.455500000000001</t>
         </is>
       </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
       <c r="E58">
-        <v>2</v>
+        <v>19.92666666666667</v>
       </c>
       <c r="F58">
-        <v>19.92666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G58">
-        <v>1.411</v>
+        <v>1.296666666666667</v>
       </c>
       <c r="H58">
-        <v>1.296666666666667</v>
+        <v>0.1685888888888888</v>
       </c>
       <c r="I58">
-        <v>0.1685888888888888</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="J58">
-        <v>92615.83884000003</v>
+        <v>95912.38071</v>
       </c>
       <c r="K58">
-        <v>95912.38071</v>
-      </c>
-      <c r="L58">
         <v>219.7694579999981</v>
       </c>
     </row>
@@ -3051,36 +2761,31 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
           <t>24.497</t>
         </is>
       </c>
+      <c r="D59">
+        <v>6</v>
+      </c>
       <c r="E59">
-        <v>6</v>
+        <v>19.92666666666667</v>
       </c>
       <c r="F59">
-        <v>19.92666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G59">
-        <v>1.411</v>
+        <v>1.296666666666667</v>
       </c>
       <c r="H59">
-        <v>1.296666666666667</v>
+        <v>0.3046888888888887</v>
       </c>
       <c r="I59">
-        <v>0.3046888888888887</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="J59">
-        <v>92615.83884000003</v>
+        <v>104632.07634</v>
       </c>
       <c r="K59">
-        <v>104632.07634</v>
-      </c>
-      <c r="L59">
         <v>801.0824999999992</v>
       </c>
     </row>
@@ -3097,36 +2802,31 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
           <t>25.379000000000001</t>
         </is>
       </c>
+      <c r="D60">
+        <v>9</v>
+      </c>
       <c r="E60">
-        <v>9</v>
+        <v>19.92666666666667</v>
       </c>
       <c r="F60">
-        <v>19.92666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G60">
-        <v>1.411</v>
+        <v>1.296666666666667</v>
       </c>
       <c r="H60">
-        <v>1.296666666666667</v>
+        <v>0.3634888888888888</v>
       </c>
       <c r="I60">
-        <v>0.3634888888888888</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="J60">
-        <v>92615.83884000003</v>
+        <v>108399.29238</v>
       </c>
       <c r="K60">
-        <v>108399.29238</v>
-      </c>
-      <c r="L60">
         <v>1052.230236</v>
       </c>
     </row>
@@ -3143,36 +2843,31 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
           <t>25.906500000000001</t>
         </is>
       </c>
+      <c r="D61">
+        <v>2</v>
+      </c>
       <c r="E61">
-        <v>2</v>
+        <v>19.71116666666667</v>
       </c>
       <c r="F61">
-        <v>19.71116666666667</v>
+        <v>1.330166666666667</v>
       </c>
       <c r="G61">
-        <v>1.330166666666667</v>
+        <v>1.328333333333333</v>
       </c>
       <c r="H61">
-        <v>1.328333333333333</v>
+        <v>0.413022222222222</v>
       </c>
       <c r="I61">
-        <v>0.413022222222222</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="J61">
-        <v>86365.83682050004</v>
+        <v>113354.6679450001</v>
       </c>
       <c r="K61">
-        <v>113354.6679450001</v>
-      </c>
-      <c r="L61">
         <v>1799.2554083</v>
       </c>
     </row>
@@ -3189,36 +2884,31 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
           <t>24.232500000000002</t>
         </is>
       </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
       <c r="E62">
-        <v>2</v>
+        <v>19.71116666666667</v>
       </c>
       <c r="F62">
-        <v>19.71116666666667</v>
+        <v>1.330166666666667</v>
       </c>
       <c r="G62">
-        <v>1.330166666666667</v>
+        <v>1.328333333333333</v>
       </c>
       <c r="H62">
-        <v>1.328333333333333</v>
+        <v>0.3014222222222221</v>
       </c>
       <c r="I62">
-        <v>0.3014222222222221</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="J62">
-        <v>86365.83682050004</v>
+        <v>106030.030725</v>
       </c>
       <c r="K62">
-        <v>106030.030725</v>
-      </c>
-      <c r="L62">
         <v>1310.946260299998</v>
       </c>
     </row>
@@ -3235,36 +2925,31 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
           <t>21.484000000000002</t>
         </is>
       </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
       <c r="E63">
-        <v>1</v>
+        <v>20.67666666666667</v>
       </c>
       <c r="F63">
-        <v>20.67666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G63">
-        <v>1.411</v>
+        <v>1.293333333333333</v>
       </c>
       <c r="H63">
-        <v>1.293333333333333</v>
+        <v>0.05382222222222215</v>
       </c>
       <c r="I63">
-        <v>0.05382222222222215</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="J63">
-        <v>96101.71434000002</v>
+        <v>91526.99616000001</v>
       </c>
       <c r="K63">
-        <v>91526.99616000001</v>
-      </c>
-      <c r="L63">
         <v>-304.9812120000007</v>
       </c>
     </row>
@@ -3281,36 +2966,31 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
           <t>26.238499999999998</t>
         </is>
       </c>
+      <c r="D64">
+        <v>6</v>
+      </c>
       <c r="E64">
-        <v>6</v>
+        <v>19.92666666666667</v>
       </c>
       <c r="F64">
-        <v>19.92666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G64">
-        <v>1.411</v>
+        <v>1.296666666666667</v>
       </c>
       <c r="H64">
-        <v>1.296666666666667</v>
+        <v>0.4207888888888886</v>
       </c>
       <c r="I64">
-        <v>0.4207888888888886</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="J64">
-        <v>92615.83884000003</v>
+        <v>112070.40597</v>
       </c>
       <c r="K64">
-        <v>112070.40597</v>
-      </c>
-      <c r="L64">
         <v>1296.971141999999</v>
       </c>
     </row>
@@ -3327,36 +3007,31 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
           <t>21.121500000000001</t>
         </is>
       </c>
+      <c r="D65">
+        <v>2</v>
+      </c>
       <c r="E65">
-        <v>2</v>
+        <v>21.71</v>
       </c>
       <c r="F65">
-        <v>21.71</v>
+        <v>1.245</v>
       </c>
       <c r="G65">
-        <v>1.245</v>
+        <v>1.258333333333333</v>
       </c>
       <c r="H65">
-        <v>1.258333333333333</v>
+        <v>-0.03923333333333332</v>
       </c>
       <c r="I65">
-        <v>-0.03923333333333332</v>
+        <v>89033.3613</v>
       </c>
       <c r="J65">
-        <v>89033.3613</v>
+        <v>87547.56142500001</v>
       </c>
       <c r="K65">
-        <v>87547.56142500001</v>
-      </c>
-      <c r="L65">
         <v>-99.0533249999998</v>
       </c>
     </row>
@@ -3373,27 +3048,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
           <t>NA</t>
         </is>
       </c>
+      <c r="D66">
+        <v>2</v>
+      </c>
       <c r="E66">
-        <v>2</v>
+        <v>20.01333333333334</v>
       </c>
       <c r="F66">
-        <v>20.01333333333334</v>
+        <v>1.348</v>
       </c>
       <c r="G66">
-        <v>1.348</v>
-      </c>
-      <c r="H66">
         <v>1.235</v>
       </c>
-      <c r="J66">
+      <c r="I66">
         <v>88865.44416000003</v>
       </c>
     </row>
@@ -3410,36 +3080,31 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
           <t>21.770499999999998</t>
         </is>
       </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
       <c r="E67">
-        <v>2</v>
+        <v>20.01333333333334</v>
       </c>
       <c r="F67">
-        <v>20.01333333333334</v>
+        <v>1.348</v>
       </c>
       <c r="G67">
-        <v>1.348</v>
+        <v>1.235</v>
       </c>
       <c r="H67">
-        <v>1.235</v>
+        <v>0.117144444444444</v>
       </c>
       <c r="I67">
-        <v>0.117144444444444</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="J67">
-        <v>88865.44416000003</v>
+        <v>88564.353345</v>
       </c>
       <c r="K67">
-        <v>88564.353345</v>
-      </c>
-      <c r="L67">
         <v>-20.07272100000215</v>
       </c>
     </row>
@@ -3456,36 +3121,31 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
           <t>25.317</t>
         </is>
       </c>
+      <c r="D68">
+        <v>2</v>
+      </c>
       <c r="E68">
-        <v>2</v>
+        <v>19.71116666666667</v>
       </c>
       <c r="F68">
-        <v>19.71116666666667</v>
+        <v>1.330166666666667</v>
       </c>
       <c r="G68">
-        <v>1.330166666666667</v>
+        <v>1.328333333333333</v>
       </c>
       <c r="H68">
-        <v>1.328333333333333</v>
+        <v>0.373722222222222</v>
       </c>
       <c r="I68">
-        <v>0.373722222222222</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="J68">
-        <v>86365.83682050004</v>
+        <v>110775.29301</v>
       </c>
       <c r="K68">
-        <v>110775.29301</v>
-      </c>
-      <c r="L68">
         <v>1627.297079299998</v>
       </c>
     </row>
@@ -3502,36 +3162,31 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
           <t>25.959</t>
         </is>
       </c>
+      <c r="D69">
+        <v>9</v>
+      </c>
       <c r="E69">
-        <v>9</v>
+        <v>20.67666666666667</v>
       </c>
       <c r="F69">
-        <v>20.67666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G69">
-        <v>1.411</v>
+        <v>1.293333333333333</v>
       </c>
       <c r="H69">
-        <v>1.293333333333333</v>
+        <v>0.3521555555555553</v>
       </c>
       <c r="I69">
-        <v>0.3521555555555553</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="J69">
-        <v>96101.71434000002</v>
+        <v>110591.57016</v>
       </c>
       <c r="K69">
-        <v>110591.57016</v>
-      </c>
-      <c r="L69">
         <v>965.9903879999988</v>
       </c>
     </row>
@@ -3548,36 +3203,31 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
           <t>27.062999999999999</t>
         </is>
       </c>
+      <c r="D70">
+        <v>6</v>
+      </c>
       <c r="E70">
-        <v>6</v>
+        <v>19.92666666666667</v>
       </c>
       <c r="F70">
-        <v>19.92666666666667</v>
+        <v>1.411</v>
       </c>
       <c r="G70">
-        <v>1.411</v>
+        <v>1.296666666666667</v>
       </c>
       <c r="H70">
-        <v>1.296666666666667</v>
+        <v>0.4757555555555553</v>
       </c>
       <c r="I70">
-        <v>0.4757555555555553</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="J70">
-        <v>92615.83884000003</v>
+        <v>115592.02686</v>
       </c>
       <c r="K70">
-        <v>115592.02686</v>
-      </c>
-      <c r="L70">
         <v>1531.745868</v>
       </c>
     </row>
@@ -3594,37 +3244,32 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
           <t>22.271000000000001</t>
         </is>
       </c>
+      <c r="D71">
+        <v>2</v>
+      </c>
       <c r="E71">
-        <v>2</v>
+        <v>16.46</v>
       </c>
       <c r="F71">
-        <v>16.46</v>
+        <v>1.224083333333333</v>
       </c>
       <c r="G71">
-        <v>1.224083333333333</v>
+        <v>1.331666666666667</v>
       </c>
       <c r="H71">
-        <v>1.343333333333333</v>
+        <v>0.3874</v>
       </c>
       <c r="I71">
-        <v>0.3874</v>
+        <v>66368.86803</v>
       </c>
       <c r="J71">
-        <v>66368.86803</v>
+        <v>97691.96420999998</v>
       </c>
       <c r="K71">
-        <v>98547.83874000001</v>
-      </c>
-      <c r="L71">
-        <v>2145.264714</v>
+        <v>2088.206411999999</v>
       </c>
     </row>
     <row r="72">
@@ -3640,37 +3285,32 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
           <t>19.956</t>
         </is>
       </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
       <c r="E72">
-        <v>2</v>
+        <v>16.46</v>
       </c>
       <c r="F72">
-        <v>16.46</v>
+        <v>1.224083333333333</v>
       </c>
       <c r="G72">
-        <v>1.224083333333333</v>
+        <v>1.331666666666667</v>
       </c>
       <c r="H72">
-        <v>1.343333333333333</v>
+        <v>0.2330666666666666</v>
       </c>
       <c r="I72">
-        <v>0.2330666666666666</v>
+        <v>66368.86803</v>
       </c>
       <c r="J72">
-        <v>66368.86803</v>
+        <v>87537.19355999999</v>
       </c>
       <c r="K72">
-        <v>88304.10264</v>
-      </c>
-      <c r="L72">
-        <v>1462.348974</v>
+        <v>1411.221701999999</v>
       </c>
     </row>
     <row r="73">
@@ -3686,37 +3326,32 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
           <t>24.664000000000001</t>
         </is>
       </c>
+      <c r="D73">
+        <v>9</v>
+      </c>
       <c r="E73">
-        <v>9</v>
+        <v>16.84833333333334</v>
       </c>
       <c r="F73">
-        <v>16.84833333333334</v>
+        <v>1.34175</v>
       </c>
       <c r="G73">
-        <v>1.34175</v>
+        <v>1.284166666666667</v>
       </c>
       <c r="H73">
-        <v>1.288333333333333</v>
+        <v>0.5210444444444443</v>
       </c>
       <c r="I73">
-        <v>0.5210444444444443</v>
+        <v>74464.99161750001</v>
       </c>
       <c r="J73">
-        <v>74464.99161750001</v>
+        <v>104329.82988</v>
       </c>
       <c r="K73">
-        <v>104668.34328</v>
-      </c>
-      <c r="L73">
-        <v>2013.556777499999</v>
+        <v>1990.989217499999</v>
       </c>
     </row>
     <row r="74">
@@ -3732,37 +3367,32 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
           <t>17.109000000000002</t>
         </is>
       </c>
+      <c r="D74">
+        <v>2</v>
+      </c>
       <c r="E74">
-        <v>2</v>
+        <v>15.95166666666666</v>
       </c>
       <c r="F74">
-        <v>15.95166666666666</v>
+        <v>1.34175</v>
       </c>
       <c r="G74">
-        <v>1.34175</v>
+        <v>1.3275</v>
       </c>
       <c r="H74">
-        <v>1.31</v>
+        <v>0.07715555555555582</v>
       </c>
       <c r="I74">
-        <v>0.07715555555555582</v>
+        <v>70501.97198249999</v>
       </c>
       <c r="J74">
-        <v>70501.97198249999</v>
+        <v>74813.978565</v>
       </c>
       <c r="K74">
-        <v>73827.73026000001</v>
-      </c>
-      <c r="L74">
-        <v>221.7172185000013</v>
+        <v>287.4671055000004</v>
       </c>
     </row>
     <row r="75">
@@ -3778,37 +3408,32 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
           <t>22.272500000000001</t>
         </is>
       </c>
+      <c r="D75">
+        <v>2</v>
+      </c>
       <c r="E75">
-        <v>2</v>
+        <v>16.46</v>
       </c>
       <c r="F75">
-        <v>16.46</v>
+        <v>1.224083333333333</v>
       </c>
       <c r="G75">
-        <v>1.224083333333333</v>
+        <v>1.331666666666667</v>
       </c>
       <c r="H75">
-        <v>1.343333333333333</v>
+        <v>0.3875</v>
       </c>
       <c r="I75">
-        <v>0.3875</v>
+        <v>66368.86803</v>
       </c>
       <c r="J75">
-        <v>66368.86803</v>
+        <v>97698.54397499999</v>
       </c>
       <c r="K75">
-        <v>98554.47614999999</v>
-      </c>
-      <c r="L75">
-        <v>2145.707207999999</v>
+        <v>2088.645062999999</v>
       </c>
     </row>
     <row r="76">
@@ -3824,37 +3449,32 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
           <t>18.845500000000001</t>
         </is>
       </c>
+      <c r="D76">
+        <v>2</v>
+      </c>
       <c r="E76">
-        <v>2</v>
+        <v>16.46</v>
       </c>
       <c r="F76">
-        <v>16.46</v>
+        <v>1.224083333333333</v>
       </c>
       <c r="G76">
-        <v>1.224083333333333</v>
+        <v>1.331666666666667</v>
       </c>
       <c r="H76">
-        <v>1.343333333333333</v>
+        <v>0.1590333333333334</v>
       </c>
       <c r="I76">
-        <v>0.1590333333333334</v>
+        <v>66368.86803</v>
       </c>
       <c r="J76">
-        <v>66368.86803</v>
+        <v>82665.97420499999</v>
       </c>
       <c r="K76">
-        <v>83390.20676999999</v>
-      </c>
-      <c r="L76">
-        <v>1134.755915999999</v>
+        <v>1086.473745</v>
       </c>
     </row>
     <row r="77">
@@ -3870,37 +3490,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
           <t>22.077500000000001</t>
         </is>
       </c>
+      <c r="D77">
+        <v>2</v>
+      </c>
       <c r="E77">
-        <v>2</v>
+        <v>16.46</v>
       </c>
       <c r="F77">
-        <v>16.46</v>
+        <v>1.224083333333333</v>
       </c>
       <c r="G77">
-        <v>1.224083333333333</v>
+        <v>1.331666666666667</v>
       </c>
       <c r="H77">
-        <v>1.343333333333333</v>
+        <v>0.3745</v>
       </c>
       <c r="I77">
-        <v>0.3745</v>
+        <v>66368.86803</v>
       </c>
       <c r="J77">
-        <v>66368.86803</v>
+        <v>96843.17452499999</v>
       </c>
       <c r="K77">
-        <v>97691.61284999999</v>
-      </c>
-      <c r="L77">
-        <v>2088.182988</v>
+        <v>2031.620433</v>
       </c>
     </row>
     <row r="78">
@@ -3916,37 +3531,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
           <t>21.9025</t>
         </is>
       </c>
+      <c r="D78">
+        <v>2</v>
+      </c>
       <c r="E78">
-        <v>2</v>
+        <v>16.84833333333334</v>
       </c>
       <c r="F78">
-        <v>16.84833333333334</v>
+        <v>1.34175</v>
       </c>
       <c r="G78">
-        <v>1.34175</v>
+        <v>1.284166666666667</v>
       </c>
       <c r="H78">
-        <v>1.288333333333333</v>
+        <v>0.3369444444444442</v>
       </c>
       <c r="I78">
-        <v>0.3369444444444442</v>
+        <v>74464.99161750001</v>
       </c>
       <c r="J78">
-        <v>74464.99161750001</v>
+        <v>92648.56061250002</v>
       </c>
       <c r="K78">
-        <v>92949.17242500001</v>
-      </c>
-      <c r="L78">
-        <v>1232.2787205</v>
+        <v>1212.237933000001</v>
       </c>
     </row>
     <row r="79">
@@ -3962,37 +3572,32 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
           <t>20.21</t>
         </is>
       </c>
+      <c r="D79">
+        <v>2</v>
+      </c>
       <c r="E79">
-        <v>2</v>
+        <v>16.84833333333334</v>
       </c>
       <c r="F79">
-        <v>16.84833333333334</v>
+        <v>1.34175</v>
       </c>
       <c r="G79">
-        <v>1.34175</v>
+        <v>1.284166666666667</v>
       </c>
       <c r="H79">
-        <v>1.288333333333333</v>
+        <v>0.224111111111111</v>
       </c>
       <c r="I79">
-        <v>0.224111111111111</v>
+        <v>74464.99161750001</v>
       </c>
       <c r="J79">
-        <v>74464.99161750001</v>
+        <v>85489.20944999999</v>
       </c>
       <c r="K79">
-        <v>85766.59170000002</v>
-      </c>
-      <c r="L79">
-        <v>753.4400055000006</v>
+        <v>734.9478554999989</v>
       </c>
     </row>
     <row r="80">
@@ -4008,37 +3613,32 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
           <t>25.229500000000002</t>
         </is>
       </c>
+      <c r="D80">
+        <v>6</v>
+      </c>
       <c r="E80">
-        <v>6</v>
+        <v>15.95166666666666</v>
       </c>
       <c r="F80">
-        <v>15.95166666666666</v>
+        <v>1.34175</v>
       </c>
       <c r="G80">
-        <v>1.34175</v>
+        <v>1.3275</v>
       </c>
       <c r="H80">
-        <v>1.31</v>
+        <v>0.6185222222222225</v>
       </c>
       <c r="I80">
-        <v>0.6185222222222225</v>
+        <v>70501.97198249999</v>
       </c>
       <c r="J80">
-        <v>70501.97198249999</v>
+        <v>110323.1791575</v>
       </c>
       <c r="K80">
-        <v>108868.82463</v>
-      </c>
-      <c r="L80">
-        <v>2557.790176500001</v>
+        <v>2654.747145</v>
       </c>
     </row>
     <row r="81">
@@ -4054,37 +3654,32 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
           <t>19.137499999999999</t>
         </is>
       </c>
+      <c r="D81">
+        <v>2</v>
+      </c>
       <c r="E81">
-        <v>2</v>
+        <v>14.23333333333333</v>
       </c>
       <c r="F81">
-        <v>14.23333333333333</v>
+        <v>1.34275</v>
       </c>
       <c r="G81">
-        <v>1.34275</v>
+        <v>1.371666666666667</v>
       </c>
       <c r="H81">
-        <v>1.353333333333333</v>
+        <v>0.3269444444444446</v>
       </c>
       <c r="I81">
-        <v>0.3269444444444446</v>
+        <v>62954.29664999999</v>
       </c>
       <c r="J81">
-        <v>62954.29664999999</v>
+        <v>86468.39212499998</v>
       </c>
       <c r="K81">
-        <v>85312.67850000001</v>
-      </c>
-      <c r="L81">
-        <v>1490.558790000001</v>
+        <v>1567.606365</v>
       </c>
     </row>
     <row r="82">
@@ -4100,37 +3695,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
           <t>22.104500000000002</t>
         </is>
       </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
       <c r="E82">
-        <v>1</v>
+        <v>15.33666666666667</v>
       </c>
       <c r="F82">
-        <v>15.33666666666667</v>
+        <v>1.34275</v>
       </c>
       <c r="G82">
-        <v>1.34275</v>
+        <v>1.3075</v>
       </c>
       <c r="H82">
-        <v>1.34</v>
+        <v>0.451188888888889</v>
       </c>
       <c r="I82">
-        <v>0.451188888888889</v>
+        <v>67834.36039500001</v>
       </c>
       <c r="J82">
-        <v>67834.36039500001</v>
+        <v>95201.98157250001</v>
       </c>
       <c r="K82">
-        <v>97568.37882</v>
-      </c>
-      <c r="L82">
-        <v>1982.267894999999</v>
+        <v>1824.5080785</v>
       </c>
     </row>
     <row r="83">
@@ -4146,37 +3736,32 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
           <t>20.862500000000001</t>
         </is>
       </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
       <c r="E83">
-        <v>2</v>
+        <v>15.68</v>
       </c>
       <c r="F83">
-        <v>15.68</v>
+        <v>1.380583333333333</v>
       </c>
       <c r="G83">
-        <v>1.380583333333333</v>
+        <v>1.284166666666667</v>
       </c>
       <c r="H83">
-        <v>1.3</v>
+        <v>0.3455000000000001</v>
       </c>
       <c r="I83">
-        <v>0.3455000000000001</v>
+        <v>71307.01871999999</v>
       </c>
       <c r="J83">
-        <v>71307.01871999999</v>
+        <v>88249.3138125</v>
       </c>
       <c r="K83">
-        <v>89337.39750000001</v>
-      </c>
-      <c r="L83">
-        <v>1202.025252000001</v>
+        <v>1129.4863395</v>
       </c>
     </row>
     <row r="84">
@@ -4192,37 +3777,32 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
           <t>17.168500000000002</t>
         </is>
       </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
       <c r="E84">
-        <v>1</v>
+        <v>14.88166666666666</v>
       </c>
       <c r="F84">
-        <v>14.88166666666666</v>
+        <v>1.380583333333333</v>
       </c>
       <c r="G84">
-        <v>1.380583333333333</v>
+        <v>1.325</v>
       </c>
       <c r="H84">
-        <v>1.298333333333333</v>
+        <v>0.1524555555555558</v>
       </c>
       <c r="I84">
-        <v>0.1524555555555558</v>
+        <v>67676.48492249998</v>
       </c>
       <c r="J84">
-        <v>67676.48492249998</v>
+        <v>74932.776675</v>
       </c>
       <c r="K84">
-        <v>73424.69563500001</v>
-      </c>
-      <c r="L84">
-        <v>383.2140475000022</v>
+        <v>483.7527835000016</v>
       </c>
     </row>
     <row r="85">
@@ -4238,37 +3818,32 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
           <t>18.312000000000001</t>
         </is>
       </c>
+      <c r="D85">
+        <v>2</v>
+      </c>
       <c r="E85">
-        <v>2</v>
+        <v>14.23333333333333</v>
       </c>
       <c r="F85">
-        <v>14.23333333333333</v>
+        <v>1.34275</v>
       </c>
       <c r="G85">
-        <v>1.34275</v>
+        <v>1.371666666666667</v>
       </c>
       <c r="H85">
-        <v>1.353333333333333</v>
+        <v>0.2719111111111114</v>
       </c>
       <c r="I85">
-        <v>0.2719111111111114</v>
+        <v>62954.29664999999</v>
       </c>
       <c r="J85">
-        <v>62954.29664999999</v>
+        <v>82738.56023999999</v>
       </c>
       <c r="K85">
-        <v>81632.69856</v>
-      </c>
-      <c r="L85">
-        <v>1245.226794000001</v>
+        <v>1318.950906</v>
       </c>
     </row>
     <row r="86">
@@ -4284,37 +3859,32 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
           <t>23.116</t>
         </is>
       </c>
+      <c r="D86">
+        <v>6</v>
+      </c>
       <c r="E86">
-        <v>6</v>
+        <v>14.23333333333333</v>
       </c>
       <c r="F86">
-        <v>14.23333333333333</v>
+        <v>1.34275</v>
       </c>
       <c r="G86">
-        <v>1.34275</v>
+        <v>1.371666666666667</v>
       </c>
       <c r="H86">
-        <v>1.353333333333333</v>
+        <v>0.5921777777777779</v>
       </c>
       <c r="I86">
-        <v>0.5921777777777779</v>
+        <v>62954.29664999999</v>
       </c>
       <c r="J86">
-        <v>62954.29664999999</v>
+        <v>104444.32932</v>
       </c>
       <c r="K86">
-        <v>103048.35408</v>
-      </c>
-      <c r="L86">
-        <v>2672.937162000001</v>
+        <v>2766.002178</v>
       </c>
     </row>
     <row r="87">
@@ -4330,37 +3900,32 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
           <t>17.729500000000002</t>
         </is>
       </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
       <c r="E87">
-        <v>1</v>
+        <v>15.33666666666667</v>
       </c>
       <c r="F87">
-        <v>15.33666666666667</v>
+        <v>1.34275</v>
       </c>
       <c r="G87">
-        <v>1.34275</v>
+        <v>1.3075</v>
       </c>
       <c r="H87">
-        <v>1.34</v>
+        <v>0.1595222222222224</v>
       </c>
       <c r="I87">
-        <v>0.1595222222222224</v>
+        <v>67834.36039500001</v>
       </c>
       <c r="J87">
-        <v>67834.36039500001</v>
+        <v>76359.2721975</v>
       </c>
       <c r="K87">
-        <v>78257.30382</v>
-      </c>
-      <c r="L87">
-        <v>694.8628949999994</v>
+        <v>568.3274534999995</v>
       </c>
     </row>
     <row r="88">
@@ -4376,37 +3941,32 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
           <t>17.349499999999999</t>
         </is>
       </c>
+      <c r="D88">
+        <v>2</v>
+      </c>
       <c r="E88">
-        <v>2</v>
+        <v>14.88166666666666</v>
       </c>
       <c r="F88">
-        <v>14.88166666666666</v>
+        <v>1.380583333333333</v>
       </c>
       <c r="G88">
-        <v>1.380583333333333</v>
+        <v>1.325</v>
       </c>
       <c r="H88">
-        <v>1.298333333333333</v>
+        <v>0.1645222222222223</v>
       </c>
       <c r="I88">
-        <v>0.1645222222222223</v>
+        <v>67676.48492249998</v>
       </c>
       <c r="J88">
-        <v>67676.48492249998</v>
+        <v>75722.76022500001</v>
       </c>
       <c r="K88">
-        <v>74198.78014500001</v>
-      </c>
-      <c r="L88">
-        <v>434.8196815000022</v>
+        <v>536.4183535000018</v>
       </c>
     </row>
     <row r="89">
@@ -4422,37 +3982,32 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
           <t>22.1325</t>
         </is>
       </c>
+      <c r="D89">
+        <v>9</v>
+      </c>
       <c r="E89">
-        <v>9</v>
+        <v>14.88166666666666</v>
       </c>
       <c r="F89">
-        <v>14.88166666666666</v>
+        <v>1.380583333333333</v>
       </c>
       <c r="G89">
-        <v>1.380583333333333</v>
+        <v>1.325</v>
       </c>
       <c r="H89">
-        <v>1.298333333333333</v>
+        <v>0.4833888888888891</v>
       </c>
       <c r="I89">
-        <v>0.4833888888888891</v>
+        <v>67676.48492249998</v>
       </c>
       <c r="J89">
-        <v>67676.48492249998</v>
+        <v>96598.402875</v>
       </c>
       <c r="K89">
-        <v>94654.28407500002</v>
-      </c>
-      <c r="L89">
-        <v>1798.519943500003</v>
+        <v>1928.127863500001</v>
       </c>
     </row>
     <row r="90">
@@ -4468,37 +4023,32 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
           <t>21.259</t>
         </is>
       </c>
+      <c r="D90">
+        <v>6</v>
+      </c>
       <c r="E90">
-        <v>6</v>
+        <v>15.445</v>
       </c>
       <c r="F90">
-        <v>15.445</v>
+        <v>1.403333333333333</v>
       </c>
       <c r="G90">
-        <v>1.403333333333333</v>
+        <v>1.3325</v>
       </c>
       <c r="H90">
-        <v>1.351666666666667</v>
+        <v>0.3876</v>
       </c>
       <c r="I90">
-        <v>0.3876</v>
+        <v>71395.7481</v>
       </c>
       <c r="J90">
-        <v>71395.7481</v>
+        <v>93311.17204500001</v>
       </c>
       <c r="K90">
-        <v>94653.35900999999</v>
-      </c>
-      <c r="L90">
-        <v>1550.507393999999</v>
+        <v>1461.028263000001</v>
       </c>
     </row>
     <row r="91">
@@ -4514,37 +4064,32 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
           <t>21.38</t>
         </is>
       </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
       <c r="E91">
-        <v>6</v>
+        <v>15.445</v>
       </c>
       <c r="F91">
-        <v>15.445</v>
+        <v>1.403333333333333</v>
       </c>
       <c r="G91">
-        <v>1.403333333333333</v>
+        <v>1.3325</v>
       </c>
       <c r="H91">
-        <v>1.351666666666667</v>
+        <v>0.3956666666666666</v>
       </c>
       <c r="I91">
-        <v>0.3956666666666666</v>
+        <v>71395.7481</v>
       </c>
       <c r="J91">
-        <v>71395.7481</v>
+        <v>93842.27189999998</v>
       </c>
       <c r="K91">
-        <v>95192.09819999998</v>
-      </c>
-      <c r="L91">
-        <v>1586.423339999999</v>
+        <v>1496.434919999999</v>
       </c>
     </row>
     <row r="92">
@@ -4560,37 +4105,32 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
           <t>17.558</t>
         </is>
       </c>
+      <c r="D92">
+        <v>1</v>
+      </c>
       <c r="E92">
-        <v>1</v>
+        <v>15.445</v>
       </c>
       <c r="F92">
-        <v>15.445</v>
+        <v>1.403333333333333</v>
       </c>
       <c r="G92">
-        <v>1.403333333333333</v>
+        <v>1.3325</v>
       </c>
       <c r="H92">
-        <v>1.351666666666667</v>
+        <v>0.1408666666666666</v>
       </c>
       <c r="I92">
-        <v>0.1408666666666666</v>
+        <v>71395.7481</v>
       </c>
       <c r="J92">
-        <v>71395.7481</v>
+        <v>77066.53929</v>
       </c>
       <c r="K92">
-        <v>78175.06362</v>
-      </c>
-      <c r="L92">
-        <v>451.9543680000003</v>
+        <v>378.0527460000002</v>
       </c>
     </row>
     <row r="93">
@@ -4606,37 +4146,32 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
           <t>21.423500000000001</t>
         </is>
       </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
       <c r="E93">
-        <v>6</v>
+        <v>15.445</v>
       </c>
       <c r="F93">
-        <v>15.445</v>
+        <v>1.403333333333333</v>
       </c>
       <c r="G93">
-        <v>1.403333333333333</v>
+        <v>1.3325</v>
       </c>
       <c r="H93">
-        <v>1.351666666666667</v>
+        <v>0.3985666666666667</v>
       </c>
       <c r="I93">
-        <v>0.3985666666666667</v>
+        <v>71395.7481</v>
       </c>
       <c r="J93">
-        <v>71395.7481</v>
+        <v>94033.20449250002</v>
       </c>
       <c r="K93">
-        <v>95385.77716500001</v>
-      </c>
-      <c r="L93">
-        <v>1599.335271000001</v>
+        <v>1509.163759500002</v>
       </c>
     </row>
     <row r="94">
@@ -4652,37 +4187,32 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
           <t>22.026499999999999</t>
         </is>
       </c>
+      <c r="D94">
+        <v>6</v>
+      </c>
       <c r="E94">
-        <v>6</v>
+        <v>15.445</v>
       </c>
       <c r="F94">
-        <v>15.445</v>
+        <v>1.403333333333333</v>
       </c>
       <c r="G94">
-        <v>1.403333333333333</v>
+        <v>1.3325</v>
       </c>
       <c r="H94">
-        <v>1.351666666666667</v>
+        <v>0.4387666666666666</v>
       </c>
       <c r="I94">
-        <v>0.4387666666666666</v>
+        <v>71395.7481</v>
       </c>
       <c r="J94">
-        <v>71395.7481</v>
+        <v>96679.92525749998</v>
       </c>
       <c r="K94">
-        <v>98070.56833499999</v>
-      </c>
-      <c r="L94">
-        <v>1778.321348999999</v>
+        <v>1685.611810499999</v>
       </c>
     </row>
   </sheetData>

--- a/Data Analysis/1_Data/carbon+bulk_dominance_2002+2017.xlsx
+++ b/Data Analysis/1_Data/carbon+bulk_dominance_2002+2017.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K94"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -387,25 +387,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>dom17_bulk</t>
+          <t>Corg_diff</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Corg_diff</t>
+          <t>Corg02_val</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Corg02_val</t>
+          <t>Corg17_val</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Corg17_val</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Corg_val_diff</t>
         </is>
@@ -437,19 +432,16 @@
         <v>1.293333333333333</v>
       </c>
       <c r="G2">
-        <v>1.303333333333333</v>
+        <v>0.1992555555555552</v>
       </c>
       <c r="H2">
-        <v>0.1992555555555552</v>
+        <v>73304.52960000002</v>
       </c>
       <c r="I2">
-        <v>73304.52960000002</v>
+        <v>86037.67692</v>
       </c>
       <c r="J2">
-        <v>86702.91668999998</v>
-      </c>
-      <c r="K2">
-        <v>893.2258059999973</v>
+        <v>848.8764879999983</v>
       </c>
     </row>
     <row r="3">
@@ -478,19 +470,16 @@
         <v>1.291083333333333</v>
       </c>
       <c r="G3">
-        <v>1.2875</v>
+        <v>0.2577555555555556</v>
       </c>
       <c r="H3">
-        <v>0.2577555555555556</v>
+        <v>75983.8692</v>
       </c>
       <c r="I3">
-        <v>75983.8692</v>
+        <v>92426.7217905</v>
       </c>
       <c r="J3">
-        <v>92170.19632500001</v>
-      </c>
-      <c r="K3">
-        <v>1079.088475000001</v>
+        <v>1096.1901727</v>
       </c>
     </row>
     <row r="4">
@@ -519,19 +508,16 @@
         <v>1.308333333333334</v>
       </c>
       <c r="G4">
-        <v>1.303333333333333</v>
+        <v>0.1037888888888889</v>
       </c>
       <c r="H4">
-        <v>0.1037888888888889</v>
+        <v>68961.58275000002</v>
       </c>
       <c r="I4">
-        <v>68961.58275000002</v>
+        <v>75670.98952500003</v>
       </c>
       <c r="J4">
-        <v>75381.80102999999</v>
-      </c>
-      <c r="K4">
-        <v>428.0145519999981</v>
+        <v>447.2937850000007</v>
       </c>
     </row>
     <row r="5">
@@ -560,19 +546,16 @@
         <v>1.308333333333334</v>
       </c>
       <c r="G5">
-        <v>1.316666666666667</v>
+        <v>-0.04523333333333308</v>
       </c>
       <c r="H5">
-        <v>-0.04523333333333308</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="I5">
-        <v>83316.30862500001</v>
+        <v>80392.21110000001</v>
       </c>
       <c r="J5">
-        <v>80904.26339999998</v>
-      </c>
-      <c r="K5">
-        <v>-160.8030150000016</v>
+        <v>-194.9398349999993</v>
       </c>
     </row>
     <row r="6">
@@ -601,19 +584,16 @@
         <v>1.266083333333333</v>
       </c>
       <c r="G6">
-        <v>1.291666666666667</v>
+        <v>-0.04667222222222212</v>
       </c>
       <c r="H6">
-        <v>-0.04667222222222212</v>
+        <v>80868.01089412501</v>
       </c>
       <c r="I6">
-        <v>80868.01089412501</v>
+        <v>77948.32840425003</v>
       </c>
       <c r="J6">
-        <v>79523.40487500001</v>
-      </c>
-      <c r="K6">
-        <v>-89.64040127499999</v>
+        <v>-194.6454993249984</v>
       </c>
     </row>
     <row r="7">
@@ -642,19 +622,16 @@
         <v>1.266083333333333</v>
       </c>
       <c r="G7">
-        <v>1.291666666666667</v>
+        <v>0.1439611111111113</v>
       </c>
       <c r="H7">
-        <v>0.1439611111111113</v>
+        <v>80868.01089412501</v>
       </c>
       <c r="I7">
-        <v>80868.01089412501</v>
+        <v>89873.811675</v>
       </c>
       <c r="J7">
-        <v>91689.86250000002</v>
-      </c>
-      <c r="K7">
-        <v>721.4567737250006</v>
+        <v>600.3867187249998</v>
       </c>
     </row>
     <row r="8">
@@ -683,19 +660,16 @@
         <v>1.266083333333333</v>
       </c>
       <c r="G8">
-        <v>1.291666666666667</v>
+        <v>-0.0004055555555555183</v>
       </c>
       <c r="H8">
-        <v>-0.0004055555555555183</v>
+        <v>80868.01089412501</v>
       </c>
       <c r="I8">
-        <v>80868.01089412501</v>
+        <v>80842.64048325</v>
       </c>
       <c r="J8">
-        <v>82476.201375</v>
-      </c>
-      <c r="K8">
-        <v>107.2126987249998</v>
+        <v>-1.691360725000656</v>
       </c>
     </row>
     <row r="9">
@@ -724,19 +698,16 @@
         <v>1.266083333333333</v>
       </c>
       <c r="G9">
-        <v>1.289166666666667</v>
+        <v>0.0339444444444446</v>
       </c>
       <c r="H9">
-        <v>0.0339444444444446</v>
+        <v>83337.97678575001</v>
       </c>
       <c r="I9">
-        <v>83337.97678575001</v>
+        <v>85461.445422</v>
       </c>
       <c r="J9">
-        <v>87019.58537999999</v>
-      </c>
-      <c r="K9">
-        <v>245.4405729499985</v>
+        <v>141.5645757499995</v>
       </c>
     </row>
     <row r="10">
@@ -765,19 +736,16 @@
         <v>1.266083333333333</v>
       </c>
       <c r="G10">
-        <v>1.289166666666667</v>
+        <v>0.1798111111111112</v>
       </c>
       <c r="H10">
-        <v>0.1798111111111112</v>
+        <v>83337.97678575001</v>
       </c>
       <c r="I10">
-        <v>83337.97678575001</v>
+        <v>94586.45238000002</v>
       </c>
       <c r="J10">
-        <v>96310.9602</v>
-      </c>
-      <c r="K10">
-        <v>864.8655609499993</v>
+        <v>749.8983729500003</v>
       </c>
     </row>
     <row r="11">
@@ -806,19 +774,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G11">
-        <v>1.298333333333333</v>
+        <v>0.2957222222222221</v>
       </c>
       <c r="H11">
-        <v>0.2957222222222221</v>
+        <v>89845.87398000002</v>
       </c>
       <c r="I11">
-        <v>89845.87398000002</v>
+        <v>108616.95441</v>
       </c>
       <c r="J11">
-        <v>109772.453925</v>
-      </c>
-      <c r="K11">
-        <v>1328.438662999998</v>
+        <v>1251.405361999999</v>
       </c>
     </row>
     <row r="12">
@@ -847,19 +812,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G12">
-        <v>1.264166666666667</v>
+        <v>-0.06656666666666666</v>
       </c>
       <c r="H12">
-        <v>-0.06656666666666666</v>
+        <v>89161.75044</v>
       </c>
       <c r="I12">
-        <v>89161.75044</v>
+        <v>84936.40597800002</v>
       </c>
       <c r="J12">
-        <v>83581.03779749999</v>
-      </c>
-      <c r="K12">
-        <v>-372.0475095000011</v>
+        <v>-281.6896307999986</v>
       </c>
     </row>
     <row r="13">
@@ -888,19 +850,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G13">
-        <v>1.264166666666667</v>
+        <v>-0.08786666666666676</v>
       </c>
       <c r="H13">
-        <v>-0.08786666666666676</v>
+        <v>89161.75044</v>
       </c>
       <c r="I13">
-        <v>89161.75044</v>
+        <v>83584.38038400002</v>
       </c>
       <c r="J13">
-        <v>82250.58708</v>
-      </c>
-      <c r="K13">
-        <v>-460.7442240000004</v>
+        <v>-371.824670399999</v>
       </c>
     </row>
     <row r="14">
@@ -929,19 +888,16 @@
         <v>1.245583333333333</v>
       </c>
       <c r="G14">
-        <v>1.225833333333333</v>
+        <v>0.3189555555555555</v>
       </c>
       <c r="H14">
-        <v>0.3189555555555555</v>
+        <v>85932.90004125002</v>
       </c>
       <c r="I14">
-        <v>85932.90004125002</v>
+        <v>105562.78766775</v>
       </c>
       <c r="J14">
-        <v>103888.9815075</v>
-      </c>
-      <c r="K14">
-        <v>1197.072097749999</v>
+        <v>1308.6591751</v>
       </c>
     </row>
     <row r="15">
@@ -970,19 +926,16 @@
         <v>1.245583333333333</v>
       </c>
       <c r="G15">
-        <v>1.2675</v>
+        <v>-0.02451111111111075</v>
       </c>
       <c r="H15">
-        <v>-0.02451111111111075</v>
+        <v>82271.01582750001</v>
       </c>
       <c r="I15">
-        <v>82271.01582750001</v>
+        <v>80762.497326</v>
       </c>
       <c r="J15">
-        <v>82183.55418000001</v>
-      </c>
-      <c r="K15">
-        <v>-5.830776500000502</v>
+        <v>-100.5679001000011</v>
       </c>
     </row>
     <row r="16">
@@ -1011,19 +964,16 @@
         <v>1.245583333333333</v>
       </c>
       <c r="G16">
-        <v>1.2675</v>
+        <v>0.1312888888888892</v>
       </c>
       <c r="H16">
-        <v>0.1312888888888892</v>
+        <v>82271.01582750001</v>
       </c>
       <c r="I16">
-        <v>82271.01582750001</v>
+        <v>90351.09498150001</v>
       </c>
       <c r="J16">
-        <v>91940.86804499998</v>
-      </c>
-      <c r="K16">
-        <v>644.6568144999978</v>
+        <v>538.6719435999995</v>
       </c>
     </row>
     <row r="17">
@@ -1052,19 +1002,16 @@
         <v>1.245583333333333</v>
       </c>
       <c r="G17">
-        <v>1.2675</v>
+        <v>0.2204888888888893</v>
       </c>
       <c r="H17">
-        <v>0.2204888888888893</v>
+        <v>82271.01582750001</v>
       </c>
       <c r="I17">
-        <v>82271.01582750001</v>
+        <v>95840.84408850002</v>
       </c>
       <c r="J17">
-        <v>97527.21205500001</v>
-      </c>
-      <c r="K17">
-        <v>1017.0797485</v>
+        <v>904.6552174000002</v>
       </c>
     </row>
     <row r="18">
@@ -1093,19 +1040,16 @@
         <v>1.181833333333334</v>
       </c>
       <c r="G18">
-        <v>1.173333333333333</v>
+        <v>0.3651166666666669</v>
       </c>
       <c r="H18">
-        <v>0.3651166666666669</v>
+        <v>75372.55243875</v>
       </c>
       <c r="I18">
-        <v>75372.55243875</v>
+        <v>96693.31564200002</v>
       </c>
       <c r="J18">
-        <v>95997.87648000001</v>
-      </c>
-      <c r="K18">
-        <v>1375.02160275</v>
+        <v>1421.384213550001</v>
       </c>
     </row>
     <row r="19">
@@ -1134,19 +1078,16 @@
         <v>1.291083333333333</v>
       </c>
       <c r="G19">
-        <v>1.2875</v>
+        <v>0.004988888888888946</v>
       </c>
       <c r="H19">
-        <v>0.004988888888888946</v>
+        <v>75983.8692</v>
       </c>
       <c r="I19">
-        <v>75983.8692</v>
+        <v>76302.12253275001</v>
       </c>
       <c r="J19">
-        <v>76090.35003750001</v>
-      </c>
-      <c r="K19">
-        <v>7.098722500000926</v>
+        <v>21.21688885000088</v>
       </c>
     </row>
     <row r="20">
@@ -1175,19 +1116,16 @@
         <v>1.308333333333334</v>
       </c>
       <c r="G20">
-        <v>1.303333333333333</v>
+        <v>0.08812222222222227</v>
       </c>
       <c r="H20">
-        <v>0.08812222222222227</v>
+        <v>68961.58275000002</v>
       </c>
       <c r="I20">
-        <v>68961.58275000002</v>
+        <v>74658.221775</v>
       </c>
       <c r="J20">
-        <v>74372.90372999999</v>
-      </c>
-      <c r="K20">
-        <v>360.7547319999983</v>
+        <v>379.7759349999988</v>
       </c>
     </row>
     <row r="21">
@@ -1216,19 +1154,16 @@
         <v>1.308333333333334</v>
       </c>
       <c r="G21">
-        <v>1.316666666666667</v>
+        <v>0.2665333333333336</v>
       </c>
       <c r="H21">
-        <v>0.2665333333333336</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="I21">
-        <v>83316.30862500001</v>
+        <v>100546.289325</v>
       </c>
       <c r="J21">
-        <v>101186.71155</v>
-      </c>
-      <c r="K21">
-        <v>1191.360195</v>
+        <v>1148.66538</v>
       </c>
     </row>
     <row r="22">
@@ -1257,19 +1192,16 @@
         <v>1.308333333333334</v>
       </c>
       <c r="G22">
-        <v>1.316666666666667</v>
+        <v>0.362466666666667</v>
       </c>
       <c r="H22">
-        <v>0.362466666666667</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="I22">
-        <v>83316.30862500001</v>
+        <v>106747.875675</v>
       </c>
       <c r="J22">
-        <v>107427.79845</v>
-      </c>
-      <c r="K22">
-        <v>1607.432655</v>
+        <v>1562.104470000002</v>
       </c>
     </row>
     <row r="23">
@@ -1298,19 +1230,16 @@
         <v>1.308333333333334</v>
       </c>
       <c r="G23">
-        <v>1.316666666666667</v>
+        <v>-0.144733333333333</v>
       </c>
       <c r="H23">
-        <v>-0.144733333333333</v>
+        <v>83316.30862500001</v>
       </c>
       <c r="I23">
-        <v>83316.30862500001</v>
+        <v>73960.05847500001</v>
       </c>
       <c r="J23">
-        <v>74431.14165000001</v>
-      </c>
-      <c r="K23">
-        <v>-592.344465</v>
+        <v>-623.7500099999995</v>
       </c>
     </row>
     <row r="24">
@@ -1339,19 +1268,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G24">
-        <v>1.298333333333333</v>
+        <v>0.2523888888888886</v>
       </c>
       <c r="H24">
-        <v>0.2523888888888886</v>
+        <v>89845.87398000002</v>
       </c>
       <c r="I24">
-        <v>89845.87398000002</v>
+        <v>105866.35461</v>
       </c>
       <c r="J24">
-        <v>106992.592425</v>
-      </c>
-      <c r="K24">
-        <v>1143.114562999998</v>
+        <v>1068.032042</v>
       </c>
     </row>
     <row r="25">
@@ -1380,19 +1306,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G25">
-        <v>1.298333333333333</v>
+        <v>0.3234555555555554</v>
       </c>
       <c r="H25">
-        <v>0.3234555555555554</v>
+        <v>89845.87398000002</v>
       </c>
       <c r="I25">
-        <v>89845.87398000002</v>
+        <v>110377.338282</v>
       </c>
       <c r="J25">
-        <v>111551.565285</v>
-      </c>
-      <c r="K25">
-        <v>1447.046086999999</v>
+        <v>1368.7642868</v>
       </c>
     </row>
     <row r="26">
@@ -1421,19 +1344,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G26">
-        <v>1.264166666666667</v>
+        <v>0.1514333333333333</v>
       </c>
       <c r="H26">
-        <v>0.1514333333333333</v>
+        <v>89161.75044</v>
       </c>
       <c r="I26">
-        <v>89161.75044</v>
+        <v>98774.038818</v>
       </c>
       <c r="J26">
-        <v>97197.8573475</v>
-      </c>
-      <c r="K26">
-        <v>535.7404604999998</v>
+        <v>640.8192251999998</v>
       </c>
     </row>
     <row r="27">
@@ -1462,19 +1382,16 @@
         <v>1.284666666666667</v>
       </c>
       <c r="G27">
-        <v>1.264166666666667</v>
+        <v>0.1916999999999999</v>
       </c>
       <c r="H27">
-        <v>0.1916999999999999</v>
+        <v>89161.75044</v>
       </c>
       <c r="I27">
-        <v>89161.75044</v>
+        <v>101329.980786</v>
       </c>
       <c r="J27">
-        <v>99713.01300749999</v>
-      </c>
-      <c r="K27">
-        <v>703.4175044999992</v>
+        <v>811.2153564000007</v>
       </c>
     </row>
     <row r="28">
@@ -1503,19 +1420,16 @@
         <v>1.26975</v>
       </c>
       <c r="G28">
-        <v>1.2975</v>
+        <v>-0.007377777777777794</v>
       </c>
       <c r="H28">
-        <v>-0.007377777777777794</v>
+        <v>78555.38199750001</v>
       </c>
       <c r="I28">
-        <v>78555.38199750001</v>
+        <v>78092.51241150001</v>
       </c>
       <c r="J28">
-        <v>79799.20051499999</v>
-      </c>
-      <c r="K28">
-        <v>82.92123449999877</v>
+        <v>-30.85797240000005</v>
       </c>
     </row>
     <row r="29">
@@ -1544,19 +1458,16 @@
         <v>1.26975</v>
       </c>
       <c r="G29">
-        <v>1.2975</v>
+        <v>0.268888888888889</v>
       </c>
       <c r="H29">
-        <v>0.268888888888889</v>
+        <v>78555.38199750001</v>
       </c>
       <c r="I29">
-        <v>78555.38199750001</v>
+        <v>95425.02654750001</v>
       </c>
       <c r="J29">
-        <v>97510.51147500002</v>
-      </c>
-      <c r="K29">
-        <v>1263.675298500001</v>
+        <v>1124.64297</v>
       </c>
     </row>
     <row r="30">
@@ -1585,19 +1496,16 @@
         <v>1.26975</v>
       </c>
       <c r="G30">
-        <v>1.2975</v>
+        <v>-0.02227777777777765</v>
       </c>
       <c r="H30">
-        <v>-0.02227777777777765</v>
+        <v>78555.38199750001</v>
       </c>
       <c r="I30">
-        <v>78555.38199750001</v>
+        <v>77157.71103375003</v>
       </c>
       <c r="J30">
-        <v>78843.96933750001</v>
-      </c>
-      <c r="K30">
-        <v>19.23915599999988</v>
+        <v>-93.17806424999823</v>
       </c>
     </row>
     <row r="31">
@@ -1626,19 +1534,16 @@
         <v>1.3415</v>
       </c>
       <c r="G31">
-        <v>1.279166666666667</v>
+        <v>0.1762944444444446</v>
       </c>
       <c r="H31">
-        <v>0.1762944444444446</v>
+        <v>82620.56023875</v>
       </c>
       <c r="I31">
-        <v>82620.56023875</v>
+        <v>94305.9756915</v>
       </c>
       <c r="J31">
-        <v>89924.01086250001</v>
-      </c>
-      <c r="K31">
-        <v>486.8967082500012</v>
+        <v>779.0276968500004</v>
       </c>
     </row>
     <row r="32">
@@ -1667,19 +1572,16 @@
         <v>1.303916666666667</v>
       </c>
       <c r="G32">
-        <v>1.266666666666667</v>
+        <v>-0.1983500000000004</v>
       </c>
       <c r="H32">
-        <v>-0.1983500000000004</v>
+        <v>87219.55238512503</v>
       </c>
       <c r="I32">
-        <v>87219.55238512503</v>
+        <v>74440.55164725</v>
       </c>
       <c r="J32">
-        <v>72313.9506</v>
-      </c>
-      <c r="K32">
-        <v>-993.7067856750024</v>
+        <v>-851.933382525002</v>
       </c>
     </row>
     <row r="33">
@@ -1708,19 +1610,16 @@
         <v>1.303916666666667</v>
       </c>
       <c r="G33">
-        <v>1.2425</v>
+        <v>0.1738</v>
       </c>
       <c r="H33">
-        <v>0.1738</v>
+        <v>94943.21865750001</v>
       </c>
       <c r="I33">
-        <v>94943.21865750001</v>
+        <v>106140.548268</v>
       </c>
       <c r="J33">
-        <v>101141.15004</v>
-      </c>
-      <c r="K33">
-        <v>413.195425499999</v>
+        <v>746.4886406999993</v>
       </c>
     </row>
     <row r="34">
@@ -1749,19 +1648,16 @@
         <v>1.283833333333333</v>
       </c>
       <c r="G34">
-        <v>1.261666666666667</v>
+        <v>0.2177166666666667</v>
       </c>
       <c r="H34">
-        <v>0.2177166666666667</v>
+        <v>81444.23303624999</v>
       </c>
       <c r="I34">
-        <v>81444.23303624999</v>
+        <v>95254.9167015</v>
       </c>
       <c r="J34">
-        <v>93610.24528500001</v>
-      </c>
-      <c r="K34">
-        <v>811.0674832500013</v>
+        <v>920.7122443500004</v>
       </c>
     </row>
     <row r="35">
@@ -1790,19 +1686,16 @@
         <v>1.283833333333333</v>
       </c>
       <c r="G35">
-        <v>1.229166666666667</v>
+        <v>-0.02337777777777793</v>
       </c>
       <c r="H35">
-        <v>-0.02337777777777793</v>
+        <v>87799.98796500004</v>
       </c>
       <c r="I35">
-        <v>87799.98796500004</v>
+        <v>86317.03721700002</v>
       </c>
       <c r="J35">
-        <v>82641.58762499999</v>
-      </c>
-      <c r="K35">
-        <v>-343.8933560000034</v>
+        <v>-98.86338320000117</v>
       </c>
     </row>
     <row r="36">
@@ -1831,19 +1724,16 @@
         <v>1.230333333333334</v>
       </c>
       <c r="G36">
-        <v>1.263333333333333</v>
+        <v>0.3813611111111113</v>
       </c>
       <c r="H36">
-        <v>0.3813611111111113</v>
+        <v>90850.11713249999</v>
       </c>
       <c r="I36">
-        <v>90850.11713249999</v>
+        <v>114033.352725</v>
       </c>
       <c r="J36">
-        <v>117091.95525</v>
-      </c>
-      <c r="K36">
-        <v>1749.455874500002</v>
+        <v>1545.549039500002</v>
       </c>
     </row>
     <row r="37">
@@ -1872,19 +1762,16 @@
         <v>1.230333333333334</v>
       </c>
       <c r="G37">
-        <v>1.230833333333333</v>
+        <v>-0.1349166666666669</v>
       </c>
       <c r="H37">
-        <v>-0.1349166666666669</v>
+        <v>92285.45475750002</v>
       </c>
       <c r="I37">
-        <v>92285.45475750002</v>
+        <v>84083.76670500002</v>
       </c>
       <c r="J37">
-        <v>84117.93783750001</v>
-      </c>
-      <c r="K37">
-        <v>-544.5011280000006</v>
+        <v>-546.7792035000001</v>
       </c>
     </row>
     <row r="38">
@@ -1913,19 +1800,16 @@
         <v>1.181833333333334</v>
       </c>
       <c r="G38">
-        <v>1.181666666666667</v>
+        <v>-0.3079999999999998</v>
       </c>
       <c r="H38">
-        <v>-0.3079999999999998</v>
+        <v>91192.56457500003</v>
       </c>
       <c r="I38">
-        <v>91192.56457500003</v>
+        <v>73207.09399500002</v>
       </c>
       <c r="J38">
-        <v>73196.77004999999</v>
-      </c>
-      <c r="K38">
-        <v>-1199.719635000002</v>
+        <v>-1199.031372000001</v>
       </c>
     </row>
     <row r="39">
@@ -1954,19 +1838,16 @@
         <v>1.181833333333334</v>
       </c>
       <c r="G39">
-        <v>1.181666666666667</v>
+        <v>0.3053333333333335</v>
       </c>
       <c r="H39">
-        <v>0.3053333333333335</v>
+        <v>91192.56457500003</v>
       </c>
       <c r="I39">
-        <v>91192.56457500003</v>
+        <v>109022.316795</v>
       </c>
       <c r="J39">
-        <v>109006.94205</v>
-      </c>
-      <c r="K39">
-        <v>1187.625164999997</v>
+        <v>1188.650147999999</v>
       </c>
     </row>
     <row r="40">
@@ -1995,19 +1876,16 @@
         <v>1.3415</v>
       </c>
       <c r="G40">
-        <v>1.3</v>
+        <v>-0.004155555555555897</v>
       </c>
       <c r="H40">
-        <v>-0.004155555555555897</v>
+        <v>84216.88822499999</v>
       </c>
       <c r="I40">
-        <v>84216.88822499999</v>
+        <v>83941.443396</v>
       </c>
       <c r="J40">
-        <v>81344.67119999998</v>
-      </c>
-      <c r="K40">
-        <v>-191.4811350000004</v>
+        <v>-18.36298859999903</v>
       </c>
     </row>
     <row r="41">
@@ -2036,19 +1914,16 @@
         <v>1.3415</v>
       </c>
       <c r="G41">
-        <v>1.3</v>
+        <v>0.1824777777777776</v>
       </c>
       <c r="H41">
-        <v>0.1824777777777776</v>
+        <v>84216.88822499999</v>
       </c>
       <c r="I41">
-        <v>84216.88822499999</v>
+        <v>96312.1567455</v>
       </c>
       <c r="J41">
-        <v>93332.69010000001</v>
-      </c>
-      <c r="K41">
-        <v>607.7201250000013</v>
+        <v>806.3512347000011</v>
       </c>
     </row>
     <row r="42">
@@ -2077,19 +1952,16 @@
         <v>1.3415</v>
       </c>
       <c r="G42">
-        <v>1.3</v>
+        <v>0.06324444444444428</v>
       </c>
       <c r="H42">
-        <v>0.06324444444444428</v>
+        <v>84216.88822499999</v>
       </c>
       <c r="I42">
-        <v>84216.88822499999</v>
+        <v>88408.952307</v>
       </c>
       <c r="J42">
-        <v>85673.97540000001</v>
-      </c>
-      <c r="K42">
-        <v>97.13914500000149</v>
+        <v>279.4709388000008</v>
       </c>
     </row>
     <row r="43">
@@ -2118,19 +1990,16 @@
         <v>1.3415</v>
       </c>
       <c r="G43">
-        <v>1.279166666666667</v>
+        <v>0.001661111111111306</v>
       </c>
       <c r="H43">
-        <v>0.001661111111111306</v>
+        <v>82620.56023875</v>
       </c>
       <c r="I43">
-        <v>82620.56023875</v>
+        <v>82730.66452199999</v>
       </c>
       <c r="J43">
-        <v>78886.55115</v>
-      </c>
-      <c r="K43">
-        <v>-248.9339392499998</v>
+        <v>7.34028554999968</v>
       </c>
     </row>
     <row r="44">
@@ -2159,19 +2028,16 @@
         <v>1.303916666666667</v>
       </c>
       <c r="G44">
-        <v>1.2425</v>
+        <v>0.1910666666666666</v>
       </c>
       <c r="H44">
-        <v>0.1910666666666666</v>
+        <v>94943.21865750001</v>
       </c>
       <c r="I44">
-        <v>94943.21865750001</v>
+        <v>107252.9795565</v>
       </c>
       <c r="J44">
-        <v>102201.183945</v>
-      </c>
-      <c r="K44">
-        <v>483.8643524999992</v>
+        <v>820.650726600002</v>
       </c>
     </row>
     <row r="45">
@@ -2200,19 +2066,16 @@
         <v>1.283833333333333</v>
       </c>
       <c r="G45">
-        <v>1.261666666666667</v>
+        <v>0.1023166666666668</v>
       </c>
       <c r="H45">
-        <v>0.1023166666666668</v>
+        <v>81444.23303624999</v>
       </c>
       <c r="I45">
-        <v>81444.23303624999</v>
+        <v>87934.60944450001</v>
       </c>
       <c r="J45">
-        <v>86416.33045500002</v>
-      </c>
-      <c r="K45">
-        <v>331.4731612500017</v>
+        <v>432.6917605500009</v>
       </c>
     </row>
     <row r="46">
@@ -2241,19 +2104,16 @@
         <v>1.283833333333333</v>
       </c>
       <c r="G46">
-        <v>1.229166666666667</v>
+        <v>0.3718888888888887</v>
       </c>
       <c r="H46">
-        <v>0.3718888888888887</v>
+        <v>87799.98796500004</v>
       </c>
       <c r="I46">
-        <v>87799.98796500004</v>
+        <v>111390.46398</v>
       </c>
       <c r="J46">
-        <v>106647.3675</v>
-      </c>
-      <c r="K46">
-        <v>1256.491968999996</v>
+        <v>1572.698400999998</v>
       </c>
     </row>
     <row r="47">
@@ -2282,19 +2142,16 @@
         <v>1.230333333333334</v>
       </c>
       <c r="G47">
-        <v>1.263333333333333</v>
+        <v>0.1614611111111112</v>
       </c>
       <c r="H47">
-        <v>0.1614611111111112</v>
+        <v>90850.11713249999</v>
       </c>
       <c r="I47">
-        <v>90850.11713249999</v>
+        <v>100665.462402</v>
       </c>
       <c r="J47">
-        <v>103365.51138</v>
-      </c>
-      <c r="K47">
-        <v>834.3596164999996</v>
+        <v>654.3563513000011</v>
       </c>
     </row>
     <row r="48">
@@ -2323,19 +2180,16 @@
         <v>1.230333333333334</v>
       </c>
       <c r="G48">
-        <v>1.230833333333333</v>
+        <v>0.2097499999999999</v>
       </c>
       <c r="H48">
-        <v>0.2097499999999999</v>
+        <v>92285.45475750002</v>
       </c>
       <c r="I48">
-        <v>92285.45475750002</v>
+        <v>105036.318765</v>
       </c>
       <c r="J48">
-        <v>105079.0048875</v>
-      </c>
-      <c r="K48">
-        <v>852.9033420000002</v>
+        <v>850.057600499999</v>
       </c>
     </row>
     <row r="49">
@@ -2364,19 +2218,16 @@
         <v>1.230333333333334</v>
       </c>
       <c r="G49">
-        <v>1.230833333333333</v>
+        <v>0.3979166666666664</v>
       </c>
       <c r="H49">
-        <v>0.3979166666666664</v>
+        <v>92285.45475750002</v>
       </c>
       <c r="I49">
-        <v>92285.45475750002</v>
+        <v>116475.11532</v>
       </c>
       <c r="J49">
-        <v>116522.4501</v>
-      </c>
-      <c r="K49">
-        <v>1615.799689499999</v>
+        <v>1612.6440375</v>
       </c>
     </row>
     <row r="50">
@@ -2405,19 +2256,16 @@
         <v>1.348</v>
       </c>
       <c r="G50">
-        <v>1.235</v>
+        <v>0.0481111111111107</v>
       </c>
       <c r="H50">
-        <v>0.0481111111111107</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="I50">
-        <v>88865.44416000003</v>
+        <v>92069.86932000001</v>
       </c>
       <c r="J50">
-        <v>84351.84615000001</v>
-      </c>
-      <c r="K50">
-        <v>-300.906534000001</v>
+        <v>213.6283439999989</v>
       </c>
     </row>
     <row r="51">
@@ -2446,19 +2294,16 @@
         <v>1.348</v>
       </c>
       <c r="G51">
-        <v>1.235</v>
+        <v>0.3011777777777773</v>
       </c>
       <c r="H51">
-        <v>0.3011777777777773</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="I51">
-        <v>88865.44416000003</v>
+        <v>108925.293672</v>
       </c>
       <c r="J51">
-        <v>99794.31579000001</v>
-      </c>
-      <c r="K51">
-        <v>728.5914419999987</v>
+        <v>1337.323300799999</v>
       </c>
     </row>
     <row r="52">
@@ -2487,19 +2332,16 @@
         <v>1.348</v>
       </c>
       <c r="G52">
-        <v>1.235</v>
+        <v>0.2819444444444441</v>
       </c>
       <c r="H52">
-        <v>0.2819444444444441</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="I52">
-        <v>88865.44416000003</v>
+        <v>107644.26366</v>
       </c>
       <c r="J52">
-        <v>98620.67182500003</v>
-      </c>
-      <c r="K52">
-        <v>650.3485109999999</v>
+        <v>1251.921299999999</v>
       </c>
     </row>
     <row r="53">
@@ -2528,19 +2370,16 @@
         <v>1.379</v>
       </c>
       <c r="G53">
-        <v>1.238333333333333</v>
+        <v>0.1559222222222225</v>
       </c>
       <c r="H53">
-        <v>0.1559222222222225</v>
+        <v>78911.78154299999</v>
       </c>
       <c r="I53">
-        <v>78911.78154299999</v>
+        <v>89535.758886</v>
       </c>
       <c r="J53">
-        <v>80402.54876999999</v>
-      </c>
-      <c r="K53">
-        <v>99.38448180000026</v>
+        <v>708.2651562000004</v>
       </c>
     </row>
     <row r="54">
@@ -2569,19 +2408,16 @@
         <v>1.379</v>
       </c>
       <c r="G54">
-        <v>1.238333333333333</v>
+        <v>0.443655555555556</v>
       </c>
       <c r="H54">
-        <v>0.443655555555556</v>
+        <v>78911.78154299999</v>
       </c>
       <c r="I54">
-        <v>78911.78154299999</v>
+        <v>109140.869502</v>
       </c>
       <c r="J54">
-        <v>98007.81488999999</v>
-      </c>
-      <c r="K54">
-        <v>1273.0688898</v>
+        <v>2015.272530600002</v>
       </c>
     </row>
     <row r="55">
@@ -2610,19 +2446,16 @@
         <v>1.330166666666667</v>
       </c>
       <c r="G55">
-        <v>1.328333333333333</v>
+        <v>0.4067888888888885</v>
       </c>
       <c r="H55">
-        <v>0.4067888888888885</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="I55">
-        <v>86365.83682050004</v>
+        <v>113101.440597</v>
       </c>
       <c r="J55">
-        <v>112945.55589</v>
-      </c>
-      <c r="K55">
-        <v>1771.981271299996</v>
+        <v>1782.373585099998</v>
       </c>
     </row>
     <row r="56">
@@ -2651,19 +2484,16 @@
         <v>1.411</v>
       </c>
       <c r="G56">
-        <v>1.293333333333333</v>
+        <v>0.04712222222222214</v>
       </c>
       <c r="H56">
-        <v>0.04712222222222214</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="I56">
-        <v>96101.71434000002</v>
+        <v>99386.958339</v>
       </c>
       <c r="J56">
-        <v>91098.84204000002</v>
-      </c>
-      <c r="K56">
-        <v>-333.5248200000002</v>
+        <v>219.0162665999989</v>
       </c>
     </row>
     <row r="57">
@@ -2692,19 +2522,16 @@
         <v>1.411</v>
       </c>
       <c r="G57">
-        <v>1.293333333333333</v>
+        <v>0.3199222222222221</v>
       </c>
       <c r="H57">
-        <v>0.3199222222222221</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="I57">
-        <v>96101.71434000002</v>
+        <v>118405.895067</v>
       </c>
       <c r="J57">
-        <v>108531.74412</v>
-      </c>
-      <c r="K57">
-        <v>828.6686520000007</v>
+        <v>1486.9453818</v>
       </c>
     </row>
     <row r="58">
@@ -2733,19 +2560,16 @@
         <v>1.411</v>
       </c>
       <c r="G58">
-        <v>1.296666666666667</v>
+        <v>0.1685888888888888</v>
       </c>
       <c r="H58">
-        <v>0.1685888888888888</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="I58">
-        <v>92615.83884000003</v>
+        <v>104369.436387</v>
       </c>
       <c r="J58">
-        <v>95912.38071</v>
-      </c>
-      <c r="K58">
-        <v>219.7694579999981</v>
+        <v>783.5731697999988</v>
       </c>
     </row>
     <row r="59">
@@ -2774,19 +2598,16 @@
         <v>1.411</v>
       </c>
       <c r="G59">
-        <v>1.296666666666667</v>
+        <v>0.3046888888888887</v>
       </c>
       <c r="H59">
-        <v>0.3046888888888887</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="I59">
-        <v>92615.83884000003</v>
+        <v>113857.989498</v>
       </c>
       <c r="J59">
-        <v>104632.07634</v>
-      </c>
-      <c r="K59">
-        <v>801.0824999999992</v>
+        <v>1416.143377199998</v>
       </c>
     </row>
     <row r="60">
@@ -2815,19 +2636,16 @@
         <v>1.411</v>
       </c>
       <c r="G60">
-        <v>1.296666666666667</v>
+        <v>0.3634888888888888</v>
       </c>
       <c r="H60">
-        <v>0.3634888888888888</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="I60">
-        <v>92615.83884000003</v>
+        <v>117957.379086</v>
       </c>
       <c r="J60">
-        <v>108399.29238</v>
-      </c>
-      <c r="K60">
-        <v>1052.230236</v>
+        <v>1689.436016399997</v>
       </c>
     </row>
     <row r="61">
@@ -2856,19 +2674,16 @@
         <v>1.330166666666667</v>
       </c>
       <c r="G61">
-        <v>1.328333333333333</v>
+        <v>0.413022222222222</v>
       </c>
       <c r="H61">
-        <v>0.413022222222222</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="I61">
-        <v>86365.83682050004</v>
+        <v>113511.1172985</v>
       </c>
       <c r="J61">
-        <v>113354.6679450001</v>
-      </c>
-      <c r="K61">
-        <v>1799.2554083</v>
+        <v>1809.685365199999</v>
       </c>
     </row>
     <row r="62">
@@ -2897,19 +2712,16 @@
         <v>1.330166666666667</v>
       </c>
       <c r="G62">
-        <v>1.328333333333333</v>
+        <v>0.3014222222222221</v>
       </c>
       <c r="H62">
-        <v>0.3014222222222221</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="I62">
-        <v>86365.83682050004</v>
+        <v>106176.3707925</v>
       </c>
       <c r="J62">
-        <v>106030.030725</v>
-      </c>
-      <c r="K62">
-        <v>1310.946260299998</v>
+        <v>1320.702264799997</v>
       </c>
     </row>
     <row r="63">
@@ -2938,19 +2750,16 @@
         <v>1.411</v>
       </c>
       <c r="G63">
-        <v>1.293333333333333</v>
+        <v>0.05382222222222215</v>
       </c>
       <c r="H63">
-        <v>0.05382222222222215</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="I63">
-        <v>96101.71434000002</v>
+        <v>99854.06565600002</v>
       </c>
       <c r="J63">
-        <v>91526.99616000001</v>
-      </c>
-      <c r="K63">
-        <v>-304.9812120000007</v>
+        <v>250.1567544</v>
       </c>
     </row>
     <row r="64">
@@ -2979,19 +2788,16 @@
         <v>1.411</v>
       </c>
       <c r="G64">
-        <v>1.296666666666667</v>
+        <v>0.4207888888888886</v>
       </c>
       <c r="H64">
-        <v>0.4207888888888886</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="I64">
-        <v>92615.83884000003</v>
+        <v>121952.192409</v>
       </c>
       <c r="J64">
-        <v>112070.40597</v>
-      </c>
-      <c r="K64">
-        <v>1296.971141999999</v>
+        <v>1955.756904599998</v>
       </c>
     </row>
     <row r="65">
@@ -3020,19 +2826,16 @@
         <v>1.245</v>
       </c>
       <c r="G65">
-        <v>1.258333333333333</v>
+        <v>-0.03923333333333332</v>
       </c>
       <c r="H65">
-        <v>-0.03923333333333332</v>
+        <v>89033.3613</v>
       </c>
       <c r="I65">
-        <v>89033.3613</v>
+        <v>86619.90514500003</v>
       </c>
       <c r="J65">
-        <v>87547.56142500001</v>
-      </c>
-      <c r="K65">
-        <v>-99.0533249999998</v>
+        <v>-160.8970769999985</v>
       </c>
     </row>
     <row r="66">
@@ -3060,10 +2863,7 @@
       <c r="F66">
         <v>1.348</v>
       </c>
-      <c r="G66">
-        <v>1.235</v>
-      </c>
-      <c r="I66">
+      <c r="H66">
         <v>88865.44416000003</v>
       </c>
     </row>
@@ -3093,19 +2893,16 @@
         <v>1.348</v>
       </c>
       <c r="G67">
-        <v>1.235</v>
+        <v>0.117144444444444</v>
       </c>
       <c r="H67">
-        <v>0.117144444444444</v>
+        <v>88865.44416000003</v>
       </c>
       <c r="I67">
-        <v>88865.44416000003</v>
+        <v>96667.81239599999</v>
       </c>
       <c r="J67">
-        <v>88564.353345</v>
-      </c>
-      <c r="K67">
-        <v>-20.07272100000215</v>
+        <v>520.1578823999977</v>
       </c>
     </row>
     <row r="68">
@@ -3134,19 +2931,16 @@
         <v>1.330166666666667</v>
       </c>
       <c r="G68">
-        <v>1.328333333333333</v>
+        <v>0.373722222222222</v>
       </c>
       <c r="H68">
-        <v>0.373722222222222</v>
+        <v>86365.83682050004</v>
       </c>
       <c r="I68">
-        <v>86365.83682050004</v>
+        <v>110928.182373</v>
       </c>
       <c r="J68">
-        <v>110775.29301</v>
-      </c>
-      <c r="K68">
-        <v>1627.297079299998</v>
+        <v>1637.489703499997</v>
       </c>
     </row>
     <row r="69">
@@ -3175,19 +2969,16 @@
         <v>1.411</v>
       </c>
       <c r="G69">
-        <v>1.293333333333333</v>
+        <v>0.3521555555555553</v>
       </c>
       <c r="H69">
-        <v>0.3521555555555553</v>
+        <v>96101.71434000002</v>
       </c>
       <c r="I69">
-        <v>96101.71434000002</v>
+        <v>120653.122806</v>
       </c>
       <c r="J69">
-        <v>110591.57016</v>
-      </c>
-      <c r="K69">
-        <v>965.9903879999988</v>
+        <v>1636.760564399999</v>
       </c>
     </row>
     <row r="70">
@@ -3216,19 +3007,16 @@
         <v>1.411</v>
       </c>
       <c r="G70">
-        <v>1.296666666666667</v>
+        <v>0.4757555555555553</v>
       </c>
       <c r="H70">
-        <v>0.4757555555555553</v>
+        <v>92615.83884000003</v>
       </c>
       <c r="I70">
-        <v>92615.83884000003</v>
+        <v>125784.331542</v>
       </c>
       <c r="J70">
-        <v>115592.02686</v>
-      </c>
-      <c r="K70">
-        <v>1531.745868</v>
+        <v>2211.232846799998</v>
       </c>
     </row>
     <row r="71">
@@ -3257,19 +3045,16 @@
         <v>1.224083333333333</v>
       </c>
       <c r="G71">
-        <v>1.331666666666667</v>
+        <v>0.3874</v>
       </c>
       <c r="H71">
-        <v>0.3874</v>
+        <v>66368.86803</v>
       </c>
       <c r="I71">
-        <v>66368.86803</v>
+        <v>89799.5783655</v>
       </c>
       <c r="J71">
-        <v>97691.96420999998</v>
-      </c>
-      <c r="K71">
-        <v>2088.206411999999</v>
+        <v>1562.0473557</v>
       </c>
     </row>
     <row r="72">
@@ -3298,19 +3083,16 @@
         <v>1.224083333333333</v>
       </c>
       <c r="G72">
-        <v>1.331666666666667</v>
+        <v>0.2330666666666666</v>
       </c>
       <c r="H72">
-        <v>0.2330666666666666</v>
+        <v>66368.86803</v>
       </c>
       <c r="I72">
-        <v>66368.86803</v>
+        <v>80465.196258</v>
       </c>
       <c r="J72">
-        <v>87537.19355999999</v>
-      </c>
-      <c r="K72">
-        <v>1411.221701999999</v>
+        <v>939.7552152</v>
       </c>
     </row>
     <row r="73">
@@ -3339,19 +3121,16 @@
         <v>1.34175</v>
       </c>
       <c r="G73">
-        <v>1.284166666666667</v>
+        <v>0.5210444444444443</v>
       </c>
       <c r="H73">
-        <v>0.5210444444444443</v>
+        <v>74464.99161750001</v>
       </c>
       <c r="I73">
-        <v>74464.99161750001</v>
+        <v>109008.085068</v>
       </c>
       <c r="J73">
-        <v>104329.82988</v>
-      </c>
-      <c r="K73">
-        <v>1990.989217499999</v>
+        <v>2302.872896699998</v>
       </c>
     </row>
     <row r="74">
@@ -3380,19 +3159,16 @@
         <v>1.34175</v>
       </c>
       <c r="G74">
-        <v>1.3275</v>
+        <v>0.07715555555555582</v>
       </c>
       <c r="H74">
-        <v>0.07715555555555582</v>
+        <v>70501.97198249999</v>
       </c>
       <c r="I74">
-        <v>70501.97198249999</v>
+        <v>75617.06647050001</v>
       </c>
       <c r="J74">
-        <v>74813.978565</v>
-      </c>
-      <c r="K74">
-        <v>287.4671055000004</v>
+        <v>341.0062992000011</v>
       </c>
     </row>
     <row r="75">
@@ -3421,19 +3197,16 @@
         <v>1.224083333333333</v>
       </c>
       <c r="G75">
-        <v>1.331666666666667</v>
+        <v>0.3875</v>
       </c>
       <c r="H75">
-        <v>0.3875</v>
+        <v>66368.86803</v>
       </c>
       <c r="I75">
-        <v>66368.86803</v>
+        <v>89805.62656125</v>
       </c>
       <c r="J75">
-        <v>97698.54397499999</v>
-      </c>
-      <c r="K75">
-        <v>2088.645062999999</v>
+        <v>1562.45056875</v>
       </c>
     </row>
     <row r="76">
@@ -3462,19 +3235,16 @@
         <v>1.224083333333333</v>
       </c>
       <c r="G76">
-        <v>1.331666666666667</v>
+        <v>0.1590333333333334</v>
       </c>
       <c r="H76">
-        <v>0.1590333333333334</v>
+        <v>66368.86803</v>
       </c>
       <c r="I76">
-        <v>66368.86803</v>
+        <v>75987.51533774998</v>
       </c>
       <c r="J76">
-        <v>82665.97420499999</v>
-      </c>
-      <c r="K76">
-        <v>1086.473745</v>
+        <v>641.2431538499989</v>
       </c>
     </row>
     <row r="77">
@@ -3503,19 +3273,16 @@
         <v>1.224083333333333</v>
       </c>
       <c r="G77">
-        <v>1.331666666666667</v>
+        <v>0.3745</v>
       </c>
       <c r="H77">
-        <v>0.3745</v>
+        <v>66368.86803</v>
       </c>
       <c r="I77">
-        <v>66368.86803</v>
+        <v>89019.36111374997</v>
       </c>
       <c r="J77">
-        <v>96843.17452499999</v>
-      </c>
-      <c r="K77">
-        <v>2031.620433</v>
+        <v>1510.032872249998</v>
       </c>
     </row>
     <row r="78">
@@ -3544,19 +3311,16 @@
         <v>1.34175</v>
       </c>
       <c r="G78">
-        <v>1.284166666666667</v>
+        <v>0.3369444444444442</v>
       </c>
       <c r="H78">
-        <v>0.3369444444444442</v>
+        <v>74464.99161750001</v>
       </c>
       <c r="I78">
-        <v>74464.99161750001</v>
+        <v>96803.01586124998</v>
       </c>
       <c r="J78">
-        <v>92648.56061250002</v>
-      </c>
-      <c r="K78">
-        <v>1212.237933000001</v>
+        <v>1489.201616249998</v>
       </c>
     </row>
     <row r="79">
@@ -3585,19 +3349,16 @@
         <v>1.34175</v>
       </c>
       <c r="G79">
-        <v>1.284166666666667</v>
+        <v>0.224111111111111</v>
       </c>
       <c r="H79">
-        <v>0.224111111111111</v>
+        <v>74464.99161750001</v>
       </c>
       <c r="I79">
-        <v>74464.99161750001</v>
+        <v>89322.63214499998</v>
       </c>
       <c r="J79">
-        <v>85489.20944999999</v>
-      </c>
-      <c r="K79">
-        <v>734.9478554999989</v>
+        <v>990.509368499998</v>
       </c>
     </row>
     <row r="80">
@@ -3626,19 +3387,16 @@
         <v>1.34175</v>
       </c>
       <c r="G80">
-        <v>1.3275</v>
+        <v>0.6185222222222225</v>
       </c>
       <c r="H80">
-        <v>0.6185222222222225</v>
+        <v>70501.97198249999</v>
       </c>
       <c r="I80">
-        <v>70501.97198249999</v>
+        <v>111507.43927275</v>
       </c>
       <c r="J80">
-        <v>110323.1791575</v>
-      </c>
-      <c r="K80">
-        <v>2654.747145</v>
+        <v>2733.697819350003</v>
       </c>
     </row>
     <row r="81">
@@ -3667,19 +3425,16 @@
         <v>1.34275</v>
       </c>
       <c r="G81">
-        <v>1.371666666666667</v>
+        <v>0.3269444444444446</v>
       </c>
       <c r="H81">
-        <v>0.3269444444444446</v>
+        <v>62954.29664999999</v>
       </c>
       <c r="I81">
-        <v>62954.29664999999</v>
+        <v>84645.51654375001</v>
       </c>
       <c r="J81">
-        <v>86468.39212499998</v>
-      </c>
-      <c r="K81">
-        <v>1567.606365</v>
+        <v>1446.081326250001</v>
       </c>
     </row>
     <row r="82">
@@ -3708,19 +3463,16 @@
         <v>1.34275</v>
       </c>
       <c r="G82">
-        <v>1.3075</v>
+        <v>0.451188888888889</v>
       </c>
       <c r="H82">
-        <v>0.451188888888889</v>
+        <v>67834.36039500001</v>
       </c>
       <c r="I82">
-        <v>67834.36039500001</v>
+        <v>97768.61243325002</v>
       </c>
       <c r="J82">
-        <v>95201.98157250001</v>
-      </c>
-      <c r="K82">
-        <v>1824.5080785</v>
+        <v>1995.616802550001</v>
       </c>
     </row>
     <row r="83">
@@ -3749,19 +3501,16 @@
         <v>1.380583333333333</v>
       </c>
       <c r="G83">
-        <v>1.284166666666667</v>
+        <v>0.3455000000000001</v>
       </c>
       <c r="H83">
-        <v>0.3455000000000001</v>
+        <v>71307.01871999999</v>
       </c>
       <c r="I83">
-        <v>71307.01871999999</v>
+        <v>94875.17079374997</v>
       </c>
       <c r="J83">
-        <v>88249.3138125</v>
-      </c>
-      <c r="K83">
-        <v>1129.4863395</v>
+        <v>1571.210138249999</v>
       </c>
     </row>
     <row r="84">
@@ -3790,19 +3539,16 @@
         <v>1.380583333333333</v>
       </c>
       <c r="G84">
-        <v>1.325</v>
+        <v>0.1524555555555558</v>
       </c>
       <c r="H84">
-        <v>0.1524555555555558</v>
+        <v>67676.48492249998</v>
       </c>
       <c r="I84">
-        <v>67676.48492249998</v>
+        <v>78076.18309274998</v>
       </c>
       <c r="J84">
-        <v>74932.776675</v>
-      </c>
-      <c r="K84">
-        <v>483.7527835000016</v>
+        <v>693.3132113500003</v>
       </c>
     </row>
     <row r="85">
@@ -3831,19 +3577,16 @@
         <v>1.34275</v>
       </c>
       <c r="G85">
-        <v>1.371666666666667</v>
+        <v>0.2719111111111114</v>
       </c>
       <c r="H85">
-        <v>0.2719111111111114</v>
+        <v>62954.29664999999</v>
       </c>
       <c r="I85">
-        <v>62954.29664999999</v>
+        <v>80994.31477200001</v>
       </c>
       <c r="J85">
-        <v>82738.56023999999</v>
-      </c>
-      <c r="K85">
-        <v>1318.950906</v>
+        <v>1202.667874800002</v>
       </c>
     </row>
     <row r="86">
@@ -3872,19 +3615,16 @@
         <v>1.34275</v>
       </c>
       <c r="G86">
-        <v>1.371666666666667</v>
+        <v>0.5921777777777779</v>
       </c>
       <c r="H86">
-        <v>0.5921777777777779</v>
+        <v>62954.29664999999</v>
       </c>
       <c r="I86">
-        <v>62954.29664999999</v>
+        <v>102242.495646</v>
       </c>
       <c r="J86">
-        <v>104444.32932</v>
-      </c>
-      <c r="K86">
-        <v>2766.002178</v>
+        <v>2619.213266400002</v>
       </c>
     </row>
     <row r="87">
@@ -3913,19 +3653,16 @@
         <v>1.34275</v>
       </c>
       <c r="G87">
-        <v>1.3075</v>
+        <v>0.1595222222222224</v>
       </c>
       <c r="H87">
-        <v>0.1595222222222224</v>
+        <v>67834.36039500001</v>
       </c>
       <c r="I87">
-        <v>67834.36039500001</v>
+        <v>78417.90649575002</v>
       </c>
       <c r="J87">
-        <v>76359.2721975</v>
-      </c>
-      <c r="K87">
-        <v>568.3274534999995</v>
+        <v>705.5697400500009</v>
       </c>
     </row>
     <row r="88">
@@ -3954,19 +3691,16 @@
         <v>1.380583333333333</v>
       </c>
       <c r="G88">
-        <v>1.325</v>
+        <v>0.1645222222222223</v>
       </c>
       <c r="H88">
-        <v>0.1645222222222223</v>
+        <v>67676.48492249998</v>
       </c>
       <c r="I88">
-        <v>67676.48492249998</v>
+        <v>78899.30620424998</v>
       </c>
       <c r="J88">
-        <v>75722.76022500001</v>
-      </c>
-      <c r="K88">
-        <v>536.4183535000018</v>
+        <v>748.1880854500001</v>
       </c>
     </row>
     <row r="89">
@@ -3995,19 +3729,16 @@
         <v>1.380583333333333</v>
       </c>
       <c r="G89">
-        <v>1.325</v>
+        <v>0.4833888888888891</v>
       </c>
       <c r="H89">
-        <v>0.4833888888888891</v>
+        <v>67676.48492249998</v>
       </c>
       <c r="I89">
-        <v>67676.48492249998</v>
+        <v>100650.67549875</v>
       </c>
       <c r="J89">
-        <v>96598.402875</v>
-      </c>
-      <c r="K89">
-        <v>1928.127863500001</v>
+        <v>2198.279371750002</v>
       </c>
     </row>
     <row r="90">
@@ -4036,19 +3767,16 @@
         <v>1.403333333333333</v>
       </c>
       <c r="G90">
-        <v>1.3325</v>
+        <v>0.3876</v>
       </c>
       <c r="H90">
-        <v>0.3876</v>
+        <v>71395.7481</v>
       </c>
       <c r="I90">
-        <v>71395.7481</v>
+        <v>98271.42821999999</v>
       </c>
       <c r="J90">
-        <v>93311.17204500001</v>
-      </c>
-      <c r="K90">
-        <v>1461.028263000001</v>
+        <v>1791.712007999999</v>
       </c>
     </row>
     <row r="91">
@@ -4077,19 +3805,16 @@
         <v>1.403333333333333</v>
       </c>
       <c r="G91">
-        <v>1.3325</v>
+        <v>0.3956666666666666</v>
       </c>
       <c r="H91">
-        <v>0.3956666666666666</v>
+        <v>71395.7481</v>
       </c>
       <c r="I91">
-        <v>71395.7481</v>
+        <v>98830.76039999998</v>
       </c>
       <c r="J91">
-        <v>93842.27189999998</v>
-      </c>
-      <c r="K91">
-        <v>1496.434919999999</v>
+        <v>1829.000819999999</v>
       </c>
     </row>
     <row r="92">
@@ -4118,19 +3843,16 @@
         <v>1.403333333333333</v>
       </c>
       <c r="G92">
-        <v>1.3325</v>
+        <v>0.1408666666666666</v>
       </c>
       <c r="H92">
-        <v>0.1408666666666666</v>
+        <v>71395.7481</v>
       </c>
       <c r="I92">
-        <v>71395.7481</v>
+        <v>81163.25963999999</v>
       </c>
       <c r="J92">
-        <v>77066.53929</v>
-      </c>
-      <c r="K92">
-        <v>378.0527460000002</v>
+        <v>651.1674359999995</v>
       </c>
     </row>
     <row r="93">
@@ -4159,19 +3881,16 @@
         <v>1.403333333333333</v>
       </c>
       <c r="G93">
-        <v>1.3325</v>
+        <v>0.3985666666666667</v>
       </c>
       <c r="H93">
-        <v>0.3985666666666667</v>
+        <v>71395.7481</v>
       </c>
       <c r="I93">
-        <v>71395.7481</v>
+        <v>99031.84262999998</v>
       </c>
       <c r="J93">
-        <v>94033.20449250002</v>
-      </c>
-      <c r="K93">
-        <v>1509.163759500002</v>
+        <v>1842.406301999999</v>
       </c>
     </row>
     <row r="94">
@@ -4200,19 +3919,16 @@
         <v>1.403333333333333</v>
       </c>
       <c r="G94">
-        <v>1.3325</v>
+        <v>0.4387666666666666</v>
       </c>
       <c r="H94">
-        <v>0.4387666666666666</v>
+        <v>71395.7481</v>
       </c>
       <c r="I94">
-        <v>71395.7481</v>
+        <v>101819.25837</v>
       </c>
       <c r="J94">
-        <v>96679.92525749998</v>
-      </c>
-      <c r="K94">
-        <v>1685.611810499999</v>
+        <v>2028.234017999999</v>
       </c>
     </row>
   </sheetData>
